--- a/artists_data.xlsx
+++ b/artists_data.xlsx
@@ -1,22 +1,29 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10222"/>
-  <workbookPr defaultThemeVersion="202300"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29912"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://brillioonline-my.sharepoint.com/personal/rajasekar_ganesan_brillio_com/Documents/Desktop/Rajasekar G/UMG/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="33" documentId="8_{A652ACD0-5135-7F4D-B45C-46ECDC52FAF1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9DE8641A-49F6-4F44-ACD7-6DDF931EFFD6}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{F44971A2-8990-43A5-95B8-78E1AE9DEF9E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1500" yWindow="1400" windowWidth="27640" windowHeight="16680" activeTab="1" xr2:uid="{FABE1C4A-AA01-3444-9480-DA5D4E9716F7}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="18980" firstSheet="3" activeTab="3" xr2:uid="{FABE1C4A-AA01-3444-9480-DA5D4E9716F7}"/>
   </bookViews>
   <sheets>
     <sheet name="Knowledge Graph" sheetId="1" r:id="rId1"/>
     <sheet name="Model training data" sheetId="2" r:id="rId2"/>
+    <sheet name="Sheet3" sheetId="4" r:id="rId3"/>
+    <sheet name="training data" sheetId="3" r:id="rId4"/>
+    <sheet name="New Artist " sheetId="5" r:id="rId5"/>
   </sheets>
-  <calcPr calcId="181029"/>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Model training data'!$A$1:$F$111</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'training data'!$A$1:$N$111</definedName>
+  </definedNames>
+  <calcPr calcId="191028"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -37,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="312" uniqueCount="206">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1225" uniqueCount="342">
   <si>
     <t>Rank </t>
   </si>
@@ -369,6 +376,9 @@
     <t>Enduring high-energy dance profile.</t>
   </si>
   <si>
+    <t>Sno</t>
+  </si>
+  <si>
     <t>Genre</t>
   </si>
   <si>
@@ -480,138 +490,138 @@
     <t>Latin Female Lead</t>
   </si>
   <si>
+    <t>41-50</t>
+  </si>
+  <si>
+    <t>Benson Boone, Teddy Swims, GloRilla, Sexyy Red, Tems, Fred again.., John Summit, Central Cee, Yeat, Ken Carson</t>
+  </si>
+  <si>
+    <t>Mixed</t>
+  </si>
+  <si>
+    <t>0.70+</t>
+  </si>
+  <si>
+    <t>2023-26 Risers</t>
+  </si>
+  <si>
     <t>Latto</t>
   </si>
   <si>
     <t>Rising Female Rap</t>
   </si>
   <si>
+    <t>51-60</t>
+  </si>
+  <si>
+    <t>Destroy Lonely, Kali Uchis, Rauw Alejandro, Feid, Grupo Frontera, Eslabon Armado, Junior H, Natanael Cano, Fuerza Regida, Xavi</t>
+  </si>
+  <si>
+    <t>Latin/Trap</t>
+  </si>
+  <si>
+    <t>0.72+</t>
+  </si>
+  <si>
+    <t>0.65+</t>
+  </si>
+  <si>
+    <t>Regional Mexican Wave</t>
+  </si>
+  <si>
     <t>Trap Leader</t>
   </si>
   <si>
+    <t>61-75</t>
+  </si>
+  <si>
+    <t>PinkPantheress, NewJeans, Stray Kids, LE SSERAFIM, TXT, ATEEZ, Laufey, Mitski, Boygenius, Ethel Cain, Dominic Fike, Djo, Beabadoobee, Steve Lacy, Omar Apollo</t>
+  </si>
+  <si>
+    <t>Pop/Indie</t>
+  </si>
+  <si>
+    <t>0.50+</t>
+  </si>
+  <si>
+    <t>0.45+</t>
+  </si>
+  <si>
+    <t>Gen-Z Favorites</t>
+  </si>
+  <si>
     <t>Melodic Trap</t>
   </si>
   <si>
+    <t>76-90</t>
+  </si>
+  <si>
+    <t>Lainey Wilson, Jelly Roll, Bailey Zimmerman, Warren Zeiders, Megan Moroney, Shaboozey, Kane Brown, Cody Johnson, Hardy, Chris Stapleton, Jordan Davis, Riley Green, Parker McCollum, Gabby Barrett, Kelsea Ballerini</t>
+  </si>
+  <si>
+    <t>0.55+</t>
+  </si>
+  <si>
+    <t>Country Boom</t>
+  </si>
+  <si>
+    <t>91-110</t>
+  </si>
+  <si>
+    <t>Don Toliver, Rod Wave, Moneybagg Yo, Lil Durk, Kodak Black, Polo G, Roddy Ricch, Brent Faiyaz, Giveon, Victoria Monét, Muni Long, Coco Jones, Tyla, Ayra Starr, Burna Boy, Wizkid, Rema, Asake, Davido, Fireboy DML</t>
+  </si>
+  <si>
+    <t>R&amp;B/Afrobeats</t>
+  </si>
+  <si>
+    <t>0.60+</t>
+  </si>
+  <si>
+    <t>0.40+</t>
+  </si>
+  <si>
+    <t>Global R&amp;B/Afro</t>
+  </si>
+  <si>
     <t>YouTube King</t>
   </si>
   <si>
+    <t>111-130</t>
+  </si>
+  <si>
+    <t>Hozier, Glass Animals, Arctic Monkeys, Cigarettes After Sex, TV Girl, The Backseat Lovers, Mt. Joy, Caamp, Noah Cyrus, Gracie Abrams, Madison Beer, Conan Gray, Girl in Red, Clairo, Phoebe Bridgers, Lucy Dacus, Julian Baker, MUNA, Maggie Rogers, King Princess</t>
+  </si>
+  <si>
+    <t>Indie/Alt</t>
+  </si>
+  <si>
+    <t>0.35+</t>
+  </si>
+  <si>
+    <t>Streaming Indie</t>
+  </si>
+  <si>
     <t>Lyricist</t>
   </si>
   <si>
+    <t>131-150</t>
+  </si>
+  <si>
+    <t>Remi Wolf, Benee, Ashnikko, Baby Keem, JID, Denzel Curry, Vince Staples, Little Simz, Kaytranada, Channel Tres, Peggy Gou, Mau P, Dom Dolla, Fisher, Chris Lake, Anyma, Charlotte de Witte, Amelie Lens, Honey Dijon, The Blessed Madonna</t>
+  </si>
+  <si>
+    <t>Electronic/Rap</t>
+  </si>
+  <si>
+    <t>0.80+</t>
+  </si>
+  <si>
+    <t>Festival Heads</t>
+  </si>
+  <si>
     <t>Performance Icon</t>
   </si>
   <si>
-    <t>41-50</t>
-  </si>
-  <si>
-    <t>Benson Boone, Teddy Swims, GloRilla, Sexyy Red, Tems, Fred again.., John Summit, Central Cee, Yeat, Ken Carson</t>
-  </si>
-  <si>
-    <t>Mixed</t>
-  </si>
-  <si>
-    <t>0.70+</t>
-  </si>
-  <si>
-    <t>2023-26 Risers</t>
-  </si>
-  <si>
-    <t>51-60</t>
-  </si>
-  <si>
-    <t>Destroy Lonely, Kali Uchis, Rauw Alejandro, Feid, Grupo Frontera, Eslabon Armado, Junior H, Natanael Cano, Fuerza Regida, Xavi</t>
-  </si>
-  <si>
-    <t>Latin/Trap</t>
-  </si>
-  <si>
-    <t>0.72+</t>
-  </si>
-  <si>
-    <t>0.65+</t>
-  </si>
-  <si>
-    <t>Regional Mexican Wave</t>
-  </si>
-  <si>
-    <t>61-75</t>
-  </si>
-  <si>
-    <t>PinkPantheress, NewJeans, Stray Kids, LE SSERAFIM, TXT, ATEEZ, Laufey, Mitski, Boygenius, Ethel Cain, Dominic Fike, Djo, Beabadoobee, Steve Lacy, Omar Apollo</t>
-  </si>
-  <si>
-    <t>Pop/Indie</t>
-  </si>
-  <si>
-    <t>0.50+</t>
-  </si>
-  <si>
-    <t>0.45+</t>
-  </si>
-  <si>
-    <t>Gen-Z Favorites</t>
-  </si>
-  <si>
-    <t>76-90</t>
-  </si>
-  <si>
-    <t>Lainey Wilson, Jelly Roll, Bailey Zimmerman, Warren Zeiders, Megan Moroney, Shaboozey, Kane Brown, Cody Johnson, Hardy, Chris Stapleton, Jordan Davis, Riley Green, Parker McCollum, Gabby Barrett, Kelsea Ballerini</t>
-  </si>
-  <si>
-    <t>0.55+</t>
-  </si>
-  <si>
-    <t>Country Boom</t>
-  </si>
-  <si>
-    <t>91-110</t>
-  </si>
-  <si>
-    <t>Don Toliver, Rod Wave, Moneybagg Yo, Lil Durk, Kodak Black, Polo G, Roddy Ricch, Brent Faiyaz, Giveon, Victoria Monét, Muni Long, Coco Jones, Tyla, Ayra Starr, Burna Boy, Wizkid, Rema, Asake, Davido, Fireboy DML</t>
-  </si>
-  <si>
-    <t>R&amp;B/Afrobeats</t>
-  </si>
-  <si>
-    <t>0.60+</t>
-  </si>
-  <si>
-    <t>0.40+</t>
-  </si>
-  <si>
-    <t>Global R&amp;B/Afro</t>
-  </si>
-  <si>
-    <t>111-130</t>
-  </si>
-  <si>
-    <t>Hozier, Glass Animals, Arctic Monkeys, Cigarettes After Sex, TV Girl, The Backseat Lovers, Mt. Joy, Caamp, Noah Cyrus, Gracie Abrams, Madison Beer, Conan Gray, Girl in Red, Clairo, Phoebe Bridgers, Lucy Dacus, Julian Baker, MUNA, Maggie Rogers, King Princess</t>
-  </si>
-  <si>
-    <t>Indie/Alt</t>
-  </si>
-  <si>
-    <t>0.35+</t>
-  </si>
-  <si>
-    <t>Streaming Indie</t>
-  </si>
-  <si>
-    <t>131-150</t>
-  </si>
-  <si>
-    <t>Remi Wolf, Benee, Ashnikko, Baby Keem, JID, Denzel Curry, Vince Staples, Little Simz, Kaytranada, Channel Tres, Peggy Gou, Mau P, Dom Dolla, Fisher, Chris Lake, Anyma, Charlotte de Witte, Amelie Lens, Honey Dijon, The Blessed Madonna</t>
-  </si>
-  <si>
-    <t>Electronic/Rap</t>
-  </si>
-  <si>
-    <t>0.80+</t>
-  </si>
-  <si>
-    <t>Festival Heads</t>
-  </si>
-  <si>
     <t>151-170</t>
   </si>
   <si>
@@ -630,6 +640,9 @@
     <t>Next-Gen Hip-Hop</t>
   </si>
   <si>
+    <t>Benson Boone</t>
+  </si>
+  <si>
     <t>171-190</t>
   </si>
   <si>
@@ -642,6 +655,9 @@
     <t>UK/International</t>
   </si>
   <si>
+    <t>Teddy Swims</t>
+  </si>
+  <si>
     <t>191-200</t>
   </si>
   <si>
@@ -654,14 +670,413 @@
     <t>One-Hit Risers</t>
   </si>
   <si>
-    <t>Sno</t>
+    <t>GloRilla</t>
+  </si>
+  <si>
+    <t>Sexyy Red</t>
+  </si>
+  <si>
+    <t>Tems</t>
+  </si>
+  <si>
+    <t>Fred again</t>
+  </si>
+  <si>
+    <t>John Summit</t>
+  </si>
+  <si>
+    <t>Fred again..</t>
+  </si>
+  <si>
+    <t>Central Cee</t>
+  </si>
+  <si>
+    <t>Yeat</t>
+  </si>
+  <si>
+    <t>Ken Carson</t>
+  </si>
+  <si>
+    <t>Destroy Lonely</t>
+  </si>
+  <si>
+    <t>Kali Uchis</t>
+  </si>
+  <si>
+    <t>Rauw Alejandro</t>
+  </si>
+  <si>
+    <t>Feid</t>
+  </si>
+  <si>
+    <t>Grupo Frontera</t>
+  </si>
+  <si>
+    <t>Eslabon Armado</t>
+  </si>
+  <si>
+    <t>Junior H</t>
+  </si>
+  <si>
+    <t>Natanael Cano</t>
+  </si>
+  <si>
+    <t>Fuerza Regida</t>
+  </si>
+  <si>
+    <t>Xavi</t>
+  </si>
+  <si>
+    <t>PinkPantheress</t>
+  </si>
+  <si>
+    <t>NewJeans</t>
+  </si>
+  <si>
+    <t>Stray Kids</t>
+  </si>
+  <si>
+    <t>LE SSERAFIM</t>
+  </si>
+  <si>
+    <t>TXT</t>
+  </si>
+  <si>
+    <t>ATEEZ</t>
+  </si>
+  <si>
+    <t>Laufey</t>
+  </si>
+  <si>
+    <t>Mitski</t>
+  </si>
+  <si>
+    <t>Boygenius</t>
+  </si>
+  <si>
+    <t>Ethel Cain</t>
+  </si>
+  <si>
+    <t>Dominic Fike</t>
+  </si>
+  <si>
+    <t>Djo</t>
+  </si>
+  <si>
+    <t>Beabadoobee</t>
+  </si>
+  <si>
+    <t>Steve Lacy</t>
+  </si>
+  <si>
+    <t>Omar Apollo</t>
+  </si>
+  <si>
+    <t>Lainey Wilson</t>
+  </si>
+  <si>
+    <t>Jelly Roll</t>
+  </si>
+  <si>
+    <t>Bailey Zimmerman</t>
+  </si>
+  <si>
+    <t>Warren Zeiders</t>
+  </si>
+  <si>
+    <t>Megan Moroney</t>
+  </si>
+  <si>
+    <t>Shaboozey</t>
+  </si>
+  <si>
+    <t>Kane Brown</t>
+  </si>
+  <si>
+    <t>Cody Johnson</t>
+  </si>
+  <si>
+    <t>Hardy</t>
+  </si>
+  <si>
+    <t>Chris Stapleton</t>
+  </si>
+  <si>
+    <t>Jordan Davis</t>
+  </si>
+  <si>
+    <t>Riley Green</t>
+  </si>
+  <si>
+    <t>Parker McCollum</t>
+  </si>
+  <si>
+    <t>Gabby Barrett</t>
+  </si>
+  <si>
+    <t>Kelsea Ballerini</t>
+  </si>
+  <si>
+    <t>Don Toliver</t>
+  </si>
+  <si>
+    <t>Rod Wave</t>
+  </si>
+  <si>
+    <t>Moneybagg Yo</t>
+  </si>
+  <si>
+    <t>Lil Durk</t>
+  </si>
+  <si>
+    <t>Kodak Black</t>
+  </si>
+  <si>
+    <t>Polo G</t>
+  </si>
+  <si>
+    <t>Roddy Ricch</t>
+  </si>
+  <si>
+    <t>Brent Faiyaz</t>
+  </si>
+  <si>
+    <t>Giveon</t>
+  </si>
+  <si>
+    <t>Victoria Monét</t>
+  </si>
+  <si>
+    <t>Muni Long</t>
+  </si>
+  <si>
+    <t>Coco Jones</t>
+  </si>
+  <si>
+    <t>Tyla</t>
+  </si>
+  <si>
+    <t>Ayra Starr</t>
+  </si>
+  <si>
+    <t>Burna Boy</t>
+  </si>
+  <si>
+    <t>Wizkid</t>
+  </si>
+  <si>
+    <t>Rema</t>
+  </si>
+  <si>
+    <t>Asake</t>
+  </si>
+  <si>
+    <t>Davido</t>
+  </si>
+  <si>
+    <t>Fireboy DML</t>
+  </si>
+  <si>
+    <t>Genre(pop)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Taylor </t>
+  </si>
+  <si>
+    <t>Jack wharff</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Energy </t>
+  </si>
+  <si>
+    <t>Followers</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MonthlyListeners </t>
+  </si>
+  <si>
+    <t xml:space="preserve">EngagementRate </t>
+  </si>
+  <si>
+    <t xml:space="preserve">GrowthRate </t>
+  </si>
+  <si>
+    <t xml:space="preserve">PlaylistCount </t>
+  </si>
+  <si>
+    <t>ViralScore</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IndustryScore </t>
+  </si>
+  <si>
+    <t>RisingScore</t>
+  </si>
+  <si>
+    <t>2025–2026 Traction Driver</t>
+  </si>
+  <si>
+    <t>Gigi Perez</t>
+  </si>
+  <si>
+    <t>Indie-Pop</t>
+  </si>
+  <si>
+    <t>"Sailor Song" reaching billion-stream status.</t>
+  </si>
+  <si>
+    <t>Alex Warren</t>
+  </si>
+  <si>
+    <t>Massive monthly listener surge (53M+) early 2026.</t>
+  </si>
+  <si>
+    <t>Country-Hip Hop</t>
+  </si>
+  <si>
+    <t>Multi-platinum crossover and 2026 award sweeps.</t>
+  </si>
+  <si>
+    <t>Lola Young</t>
+  </si>
+  <si>
+    <t>Soul / R&amp;B</t>
+  </si>
+  <si>
+    <t>2026 Grammy Best New Artist nominee/winner.</t>
+  </si>
+  <si>
+    <t>ADÉLA</t>
+  </si>
+  <si>
+    <t>Dream Academy breakout; viral single "SUPERSCAR".</t>
+  </si>
+  <si>
+    <t>Vincent Mason</t>
+  </si>
+  <si>
+    <t>"Damned If I Do" viral success; 2026 Tour riser.</t>
+  </si>
+  <si>
+    <t>Sawyer Hill</t>
+  </si>
+  <si>
+    <t>Grunge Rock</t>
+  </si>
+  <si>
+    <t>Leading the 2026 baritone-rock revival.</t>
+  </si>
+  <si>
+    <t>2hollis</t>
+  </si>
+  <si>
+    <t>Experimental Pop</t>
+  </si>
+  <si>
+    <t>Digital disruptor; 2025 opening for major tours.</t>
+  </si>
+  <si>
+    <t>Chloe Qisha</t>
+  </si>
+  <si>
+    <t>2026 TikTok bedroom-pop breakout.</t>
+  </si>
+  <si>
+    <t>Oskar med k</t>
+  </si>
+  <si>
+    <t>Chill House</t>
+  </si>
+  <si>
+    <t>2026 North American tour; Tomorrowland favorite.</t>
+  </si>
+  <si>
+    <t>Ty Myers</t>
+  </si>
+  <si>
+    <t>17-year-old prodigy; 2026 festival main-stager.</t>
+  </si>
+  <si>
+    <t>Annahstasia</t>
+  </si>
+  <si>
+    <t>Filigree Folk</t>
+  </si>
+  <si>
+    <t>Cinematic folk; 2026 Ticketmaster "Fresh List".</t>
+  </si>
+  <si>
+    <t>Sienna Spiro</t>
+  </si>
+  <si>
+    <t>Pop-Soul</t>
+  </si>
+  <si>
+    <t>Vocal powerhouse rising in early 2026 charts.</t>
+  </si>
+  <si>
+    <t>Hurricane Wisdom</t>
+  </si>
+  <si>
+    <t>Melodic Rap</t>
+  </si>
+  <si>
+    <t>2025 Florida scene breakout gaining US traction.</t>
+  </si>
+  <si>
+    <t>Debbii Dawson</t>
+  </si>
+  <si>
+    <t>Heritage-blending folk; 2025–26 tour success.</t>
+  </si>
+  <si>
+    <t>Fcukers</t>
+  </si>
+  <si>
+    <t>2025–26 NYC club scene to global festival rise.</t>
+  </si>
+  <si>
+    <t>Mk.gee</t>
+  </si>
+  <si>
+    <t>Lo-fi / Alt</t>
+  </si>
+  <si>
+    <t>2025 critical darling; 2026 mainstream influencer.</t>
+  </si>
+  <si>
+    <t>Jack Wharff</t>
+  </si>
+  <si>
+    <t>Folk-Rock</t>
+  </si>
+  <si>
+    <t>2026 rising songwriter with "unplugged" appeal.</t>
+  </si>
+  <si>
+    <t>Cameron Whitcomb</t>
+  </si>
+  <si>
+    <t>Rugged Country</t>
+  </si>
+  <si>
+    <t>2026 breakout in the "Outlaw" country subgenre.</t>
+  </si>
+  <si>
+    <t>Lexa Gates</t>
+  </si>
+  <si>
+    <t>Alt-Hip Hop</t>
+  </si>
+  <si>
+    <t>2025 "Vibe" rap viral tracks into 2026 albums.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="8">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -697,6 +1112,21 @@
       <name val="Arial"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF242424"/>
+      <name val="Aptos Narrow"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
+      <name val="Aptos Narrow"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Aptos Narrow"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -719,12 +1149,16 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="11" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -1061,16 +1495,16 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7CB1B08C-F52D-014E-9664-504E9DD6E9C3}">
   <dimension ref="A1:F41"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.95"/>
   <cols>
-    <col min="2" max="2" width="17.33203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="17.375" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="19" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="16" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="17.1640625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="69.33203125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="17.125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="69.375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:6" ht="18">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1090,7 +1524,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:6" ht="18">
       <c r="A2" s="2">
         <v>1</v>
       </c>
@@ -1110,7 +1544,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="3" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:6" ht="18">
       <c r="A3" s="2">
         <v>2</v>
       </c>
@@ -1130,7 +1564,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="4" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:6" ht="18">
       <c r="A4" s="2">
         <v>3</v>
       </c>
@@ -1150,7 +1584,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="5" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:6" ht="18">
       <c r="A5" s="2">
         <v>4</v>
       </c>
@@ -1170,7 +1604,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="6" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:6" ht="18">
       <c r="A6" s="2">
         <v>5</v>
       </c>
@@ -1190,7 +1624,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="7" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:6" ht="18">
       <c r="A7" s="2">
         <v>6</v>
       </c>
@@ -1210,7 +1644,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="8" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:6" ht="18">
       <c r="A8" s="2">
         <v>7</v>
       </c>
@@ -1230,7 +1664,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="9" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:6" ht="18">
       <c r="A9" s="2">
         <v>8</v>
       </c>
@@ -1250,7 +1684,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="10" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:6" ht="18">
       <c r="A10" s="2">
         <v>9</v>
       </c>
@@ -1270,7 +1704,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="11" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:6" ht="18">
       <c r="A11" s="2">
         <v>10</v>
       </c>
@@ -1290,7 +1724,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="12" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:6" ht="18">
       <c r="A12" s="2">
         <v>11</v>
       </c>
@@ -1310,7 +1744,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="13" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:6" ht="18">
       <c r="A13" s="2">
         <v>12</v>
       </c>
@@ -1330,7 +1764,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="14" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:6" ht="18">
       <c r="A14" s="2">
         <v>13</v>
       </c>
@@ -1350,7 +1784,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="15" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:6" ht="18">
       <c r="A15" s="2">
         <v>14</v>
       </c>
@@ -1370,7 +1804,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="16" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:6" ht="18">
       <c r="A16" s="2">
         <v>15</v>
       </c>
@@ -1390,7 +1824,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="17" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:6" ht="18">
       <c r="A17" s="2">
         <v>16</v>
       </c>
@@ -1410,7 +1844,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="18" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:6" ht="18">
       <c r="A18" s="2">
         <v>17</v>
       </c>
@@ -1430,7 +1864,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="19" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:6" ht="18">
       <c r="A19" s="2">
         <v>18</v>
       </c>
@@ -1450,7 +1884,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="20" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:6" ht="18">
       <c r="A20" s="2">
         <v>19</v>
       </c>
@@ -1470,7 +1904,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="21" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:6" ht="18">
       <c r="A21" s="2">
         <v>20</v>
       </c>
@@ -1490,7 +1924,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="22" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:6" ht="18">
       <c r="A22" s="2">
         <v>21</v>
       </c>
@@ -1510,7 +1944,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="23" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:6" ht="18">
       <c r="A23" s="2">
         <v>22</v>
       </c>
@@ -1530,7 +1964,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="24" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:6" ht="18">
       <c r="A24" s="2">
         <v>23</v>
       </c>
@@ -1550,7 +1984,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="25" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:6" ht="18">
       <c r="A25" s="2">
         <v>24</v>
       </c>
@@ -1570,7 +2004,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="26" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:6" ht="18">
       <c r="A26" s="2">
         <v>25</v>
       </c>
@@ -1590,7 +2024,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="27" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:6" ht="18">
       <c r="A27" s="2">
         <v>26</v>
       </c>
@@ -1610,7 +2044,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="28" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:6" ht="18">
       <c r="A28" s="2">
         <v>27</v>
       </c>
@@ -1630,7 +2064,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="29" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:6" ht="18">
       <c r="A29" s="2">
         <v>28</v>
       </c>
@@ -1650,7 +2084,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="30" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:6" ht="18">
       <c r="A30" s="2">
         <v>29</v>
       </c>
@@ -1670,7 +2104,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="31" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:6" ht="18">
       <c r="A31" s="2">
         <v>30</v>
       </c>
@@ -1690,7 +2124,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="32" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:6" ht="18">
       <c r="A32" s="2">
         <v>31</v>
       </c>
@@ -1710,7 +2144,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="33" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:6" ht="18">
       <c r="A33" s="2">
         <v>32</v>
       </c>
@@ -1730,7 +2164,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="34" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:6" ht="18">
       <c r="A34" s="2">
         <v>33</v>
       </c>
@@ -1750,7 +2184,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="35" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:6" ht="18">
       <c r="A35" s="2">
         <v>34</v>
       </c>
@@ -1770,7 +2204,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="36" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:6" ht="18">
       <c r="A36" s="2">
         <v>35</v>
       </c>
@@ -1790,7 +2224,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="37" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:6" ht="18">
       <c r="A37" s="2">
         <v>36</v>
       </c>
@@ -1810,7 +2244,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="38" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:6" ht="18">
       <c r="A38" s="2">
         <v>37</v>
       </c>
@@ -1830,7 +2264,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="39" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:6" ht="18">
       <c r="A39" s="2">
         <v>38</v>
       </c>
@@ -1850,7 +2284,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="40" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:6" ht="18">
       <c r="A40" s="2">
         <v>39</v>
       </c>
@@ -1870,7 +2304,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="41" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:6" ht="18">
       <c r="A41" s="2">
         <v>40</v>
       </c>
@@ -1939,38 +2373,46 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CB2143CE-4BEA-1F43-9B14-FF0CEB6C4E85}">
-  <dimension ref="A1:F52"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:N111"/>
+  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.95"/>
   <cols>
-    <col min="1" max="1" width="10" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="43.1640625" customWidth="1"/>
+    <col min="1" max="1" width="5.625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="56.875" customWidth="1"/>
     <col min="3" max="3" width="24.5" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="9.1640625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="10.1640625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="27.1640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10.125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="20.625" customWidth="1"/>
+    <col min="7" max="7" width="33.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:14" ht="18">
       <c r="A1" s="4" t="s">
-        <v>205</v>
+        <v>110</v>
       </c>
       <c r="B1" s="4" t="s">
         <v>1</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="F1" s="4" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+        <v>114</v>
+      </c>
+      <c r="H1" s="5"/>
+      <c r="I1" s="5"/>
+      <c r="J1" s="5"/>
+      <c r="K1" s="5"/>
+      <c r="L1" s="5"/>
+      <c r="M1" s="5"/>
+      <c r="N1" s="5"/>
+    </row>
+    <row r="2" spans="1:14" ht="18">
       <c r="A2" s="2">
         <v>1</v>
       </c>
@@ -1987,10 +2429,11 @@
         <v>0.38</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+        <v>115</v>
+      </c>
+      <c r="H2" s="6"/>
+    </row>
+    <row r="3" spans="1:14" ht="18">
       <c r="A3" s="2">
         <v>2</v>
       </c>
@@ -2007,10 +2450,17 @@
         <v>0.45</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+        <v>116</v>
+      </c>
+      <c r="H3" s="5"/>
+      <c r="I3" s="5"/>
+      <c r="J3" s="5"/>
+      <c r="K3" s="5"/>
+      <c r="L3" s="5"/>
+      <c r="M3" s="5"/>
+      <c r="N3" s="5"/>
+    </row>
+    <row r="4" spans="1:14" ht="18">
       <c r="A4" s="2">
         <v>3</v>
       </c>
@@ -2027,10 +2477,17 @@
         <v>0.57999999999999996</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+        <v>117</v>
+      </c>
+      <c r="H4" s="5"/>
+      <c r="I4" s="5"/>
+      <c r="J4" s="5"/>
+      <c r="K4" s="5"/>
+      <c r="L4" s="5"/>
+      <c r="M4" s="5"/>
+      <c r="N4" s="5"/>
+    </row>
+    <row r="5" spans="1:14" ht="18">
       <c r="A5" s="2">
         <v>4</v>
       </c>
@@ -2047,10 +2504,18 @@
         <v>0.42</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+        <v>118</v>
+      </c>
+      <c r="G5" s="7"/>
+      <c r="H5" s="8"/>
+      <c r="I5" s="7"/>
+      <c r="J5" s="7"/>
+      <c r="K5" s="7"/>
+      <c r="L5" s="7"/>
+      <c r="M5" s="7"/>
+      <c r="N5" s="7"/>
+    </row>
+    <row r="6" spans="1:14" ht="18">
       <c r="A6" s="2">
         <v>5</v>
       </c>
@@ -2067,10 +2532,18 @@
         <v>0.65</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+        <v>119</v>
+      </c>
+      <c r="G6" s="7"/>
+      <c r="H6" s="8"/>
+      <c r="I6" s="7"/>
+      <c r="J6" s="7"/>
+      <c r="K6" s="7"/>
+      <c r="L6" s="7"/>
+      <c r="M6" s="7"/>
+      <c r="N6" s="7"/>
+    </row>
+    <row r="7" spans="1:14" ht="18">
       <c r="A7" s="2">
         <v>6</v>
       </c>
@@ -2087,10 +2560,18 @@
         <v>0.25</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+        <v>120</v>
+      </c>
+      <c r="G7" s="7"/>
+      <c r="H7" s="7"/>
+      <c r="I7" s="7"/>
+      <c r="J7" s="7"/>
+      <c r="K7" s="7"/>
+      <c r="L7" s="7"/>
+      <c r="M7" s="7"/>
+      <c r="N7" s="7"/>
+    </row>
+    <row r="8" spans="1:14" ht="18">
       <c r="A8" s="2">
         <v>7</v>
       </c>
@@ -2107,10 +2588,18 @@
         <v>0.45</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+        <v>121</v>
+      </c>
+      <c r="G8" s="7"/>
+      <c r="H8" s="7"/>
+      <c r="I8" s="7"/>
+      <c r="J8" s="7"/>
+      <c r="K8" s="7"/>
+      <c r="L8" s="7"/>
+      <c r="M8" s="7"/>
+      <c r="N8" s="7"/>
+    </row>
+    <row r="9" spans="1:14" ht="18">
       <c r="A9" s="2">
         <v>8</v>
       </c>
@@ -2127,10 +2616,18 @@
         <v>0.35</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+        <v>122</v>
+      </c>
+      <c r="G9" s="7"/>
+      <c r="H9" s="7"/>
+      <c r="I9" s="7"/>
+      <c r="J9" s="7"/>
+      <c r="K9" s="7"/>
+      <c r="L9" s="7"/>
+      <c r="M9" s="7"/>
+      <c r="N9" s="7"/>
+    </row>
+    <row r="10" spans="1:14" ht="18">
       <c r="A10" s="2">
         <v>9</v>
       </c>
@@ -2147,10 +2644,18 @@
         <v>0.22</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+        <v>123</v>
+      </c>
+      <c r="G10" s="7"/>
+      <c r="H10" s="7"/>
+      <c r="I10" s="7"/>
+      <c r="J10" s="7"/>
+      <c r="K10" s="7"/>
+      <c r="L10" s="7"/>
+      <c r="M10" s="7"/>
+      <c r="N10" s="7"/>
+    </row>
+    <row r="11" spans="1:14" ht="18">
       <c r="A11" s="2">
         <v>10</v>
       </c>
@@ -2167,10 +2672,18 @@
         <v>0.48</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+        <v>124</v>
+      </c>
+      <c r="G11" s="7"/>
+      <c r="H11" s="7"/>
+      <c r="I11" s="7"/>
+      <c r="J11" s="7"/>
+      <c r="K11" s="7"/>
+      <c r="L11" s="7"/>
+      <c r="M11" s="7"/>
+      <c r="N11" s="7"/>
+    </row>
+    <row r="12" spans="1:14" ht="18">
       <c r="A12" s="2">
         <v>11</v>
       </c>
@@ -2187,10 +2700,10 @@
         <v>0.7</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14" ht="18">
       <c r="A13" s="2">
         <v>12</v>
       </c>
@@ -2207,10 +2720,10 @@
         <v>0.35</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14" ht="18">
       <c r="A14" s="2">
         <v>13</v>
       </c>
@@ -2218,7 +2731,7 @@
         <v>100</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="D14" s="2">
         <v>0.72</v>
@@ -2227,10 +2740,10 @@
         <v>0.75</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14" ht="18">
       <c r="A15" s="2">
         <v>14</v>
       </c>
@@ -2247,10 +2760,10 @@
         <v>0.52</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14" ht="18">
       <c r="A16" s="2">
         <v>15</v>
       </c>
@@ -2267,10 +2780,10 @@
         <v>0.32</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" ht="18">
       <c r="A17" s="2">
         <v>16</v>
       </c>
@@ -2287,10 +2800,10 @@
         <v>0.78</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" ht="18">
       <c r="A18" s="2">
         <v>17</v>
       </c>
@@ -2307,10 +2820,10 @@
         <v>0.5</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" ht="18">
       <c r="A19" s="2">
         <v>18</v>
       </c>
@@ -2327,10 +2840,10 @@
         <v>0.6</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" ht="18">
       <c r="A20" s="2">
         <v>19</v>
       </c>
@@ -2347,10 +2860,10 @@
         <v>0.68</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" ht="18">
       <c r="A21" s="2">
         <v>20</v>
       </c>
@@ -2367,10 +2880,10 @@
         <v>0.57999999999999996</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" ht="18">
       <c r="A22" s="2">
         <v>21</v>
       </c>
@@ -2387,18 +2900,18 @@
         <v>0.38</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="23" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" ht="18">
       <c r="A23" s="2">
         <v>22</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="D23" s="2">
         <v>0.65</v>
@@ -2407,10 +2920,10 @@
         <v>0.4</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="24" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" ht="18">
       <c r="A24" s="2">
         <v>23</v>
       </c>
@@ -2427,10 +2940,10 @@
         <v>0.68</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="25" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" ht="18">
       <c r="A25" s="2">
         <v>24</v>
       </c>
@@ -2447,10 +2960,10 @@
         <v>0.28000000000000003</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="26" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" ht="18">
       <c r="A26" s="2">
         <v>25</v>
       </c>
@@ -2467,10 +2980,10 @@
         <v>0.2</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="27" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" ht="18">
       <c r="A27" s="2">
         <v>26</v>
       </c>
@@ -2487,10 +3000,10 @@
         <v>0.62</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="28" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" ht="18">
       <c r="A28" s="2">
         <v>27</v>
       </c>
@@ -2507,10 +3020,10 @@
         <v>0.85</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="29" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" ht="18">
       <c r="A29" s="2">
         <v>28</v>
       </c>
@@ -2527,10 +3040,10 @@
         <v>0.65</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="30" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" ht="18">
       <c r="A30" s="2">
         <v>29</v>
       </c>
@@ -2547,10 +3060,10 @@
         <v>0.62</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="31" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" ht="18">
       <c r="A31" s="2">
         <v>30</v>
       </c>
@@ -2567,10 +3080,10 @@
         <v>0.6</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="32" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" ht="18">
       <c r="A32" s="2">
         <v>31</v>
       </c>
@@ -2587,15 +3100,15 @@
         <v>0.5</v>
       </c>
       <c r="F32" s="2" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="33" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="33" spans="1:14" ht="18">
       <c r="A33" s="2">
         <v>32</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="C33" s="2" t="s">
         <v>49</v>
@@ -2607,10 +3120,10 @@
         <v>0.55000000000000004</v>
       </c>
       <c r="F33" s="2" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="34" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="34" spans="1:14" ht="18">
       <c r="A34" s="2">
         <v>33</v>
       </c>
@@ -2627,15 +3140,33 @@
         <v>0.72</v>
       </c>
       <c r="F34" s="2" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="35" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+        <v>147</v>
+      </c>
+      <c r="I34" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="J34" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="K34" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="L34" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="M34" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="N34" s="2" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="35" spans="1:14" ht="18">
       <c r="A35" s="2">
         <v>34</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>147</v>
+        <v>153</v>
       </c>
       <c r="C35" s="2" t="s">
         <v>31</v>
@@ -2647,10 +3178,28 @@
         <v>0.6</v>
       </c>
       <c r="F35" s="2" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="36" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+        <v>154</v>
+      </c>
+      <c r="I35" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="J35" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="K35" s="2" t="s">
+        <v>157</v>
+      </c>
+      <c r="L35" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="M35" s="2" t="s">
+        <v>159</v>
+      </c>
+      <c r="N35" s="2" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="36" spans="1:14" ht="18">
       <c r="A36" s="2">
         <v>35</v>
       </c>
@@ -2667,10 +3216,28 @@
         <v>0.25</v>
       </c>
       <c r="F36" s="2" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="37" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+        <v>161</v>
+      </c>
+      <c r="I36" s="2" t="s">
+        <v>162</v>
+      </c>
+      <c r="J36" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="K36" s="2" t="s">
+        <v>164</v>
+      </c>
+      <c r="L36" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="M36" s="2" t="s">
+        <v>166</v>
+      </c>
+      <c r="N36" s="2" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="37" spans="1:14" ht="18">
       <c r="A37" s="2">
         <v>36</v>
       </c>
@@ -2687,10 +3254,28 @@
         <v>0.4</v>
       </c>
       <c r="F37" s="2" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="38" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+        <v>168</v>
+      </c>
+      <c r="I37" s="2" t="s">
+        <v>169</v>
+      </c>
+      <c r="J37" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="K37" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="L37" s="2" t="s">
+        <v>159</v>
+      </c>
+      <c r="M37" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="N37" s="2" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="38" spans="1:14" ht="18">
       <c r="A38" s="2">
         <v>37</v>
       </c>
@@ -2707,10 +3292,28 @@
         <v>0.35</v>
       </c>
       <c r="F38" s="2" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="39" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+        <v>118</v>
+      </c>
+      <c r="I38" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="J38" s="1" t="s">
+        <v>174</v>
+      </c>
+      <c r="K38" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="L38" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="M38" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="N38" s="2" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="39" spans="1:14" ht="18">
       <c r="A39" s="2">
         <v>38</v>
       </c>
@@ -2727,10 +3330,28 @@
         <v>0.38</v>
       </c>
       <c r="F39" s="2" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="40" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+        <v>179</v>
+      </c>
+      <c r="I39" s="2" t="s">
+        <v>180</v>
+      </c>
+      <c r="J39" s="1" t="s">
+        <v>181</v>
+      </c>
+      <c r="K39" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="L39" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="M39" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="N39" s="2" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="40" spans="1:14" ht="18">
       <c r="A40" s="2">
         <v>39</v>
       </c>
@@ -2747,10 +3368,28 @@
         <v>0.42</v>
       </c>
       <c r="F40" s="2" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="41" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+        <v>185</v>
+      </c>
+      <c r="I40" s="2" t="s">
+        <v>186</v>
+      </c>
+      <c r="J40" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="K40" s="2" t="s">
+        <v>188</v>
+      </c>
+      <c r="L40" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="M40" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="N40" s="2" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="41" spans="1:14" ht="18">
       <c r="A41" s="2">
         <v>40</v>
       </c>
@@ -2767,211 +3406,6903 @@
         <v>0.6</v>
       </c>
       <c r="F41" s="2" t="s">
+        <v>191</v>
+      </c>
+      <c r="I41" s="2" t="s">
+        <v>192</v>
+      </c>
+      <c r="J41" s="1" t="s">
+        <v>193</v>
+      </c>
+      <c r="K41" s="2" t="s">
+        <v>194</v>
+      </c>
+      <c r="L41" s="2" t="s">
+        <v>195</v>
+      </c>
+      <c r="M41" s="2" t="s">
+        <v>196</v>
+      </c>
+      <c r="N41" s="2" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="42" spans="1:14" ht="18">
+      <c r="A42" s="2">
+        <v>41</v>
+      </c>
+      <c r="B42" t="s">
+        <v>198</v>
+      </c>
+      <c r="C42" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="D42" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="E42" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="F42" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="I42" s="2" t="s">
+        <v>199</v>
+      </c>
+      <c r="J42" s="1" t="s">
+        <v>200</v>
+      </c>
+      <c r="K42" s="2" t="s">
+        <v>201</v>
+      </c>
+      <c r="L42" s="2" t="s">
+        <v>159</v>
+      </c>
+      <c r="M42" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="N42" s="2" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="43" spans="1:14" ht="18">
+      <c r="A43" s="2">
+        <v>42</v>
+      </c>
+      <c r="B43" t="s">
+        <v>203</v>
+      </c>
+      <c r="C43" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="D43" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="E43" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="F43" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="I43" s="2" t="s">
+        <v>204</v>
+      </c>
+      <c r="J43" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="K43" s="2" t="s">
+        <v>206</v>
+      </c>
+      <c r="L43" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="M43" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="N43" s="2" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="44" spans="1:14" ht="18">
+      <c r="A44" s="2">
+        <v>43</v>
+      </c>
+      <c r="B44" t="s">
+        <v>208</v>
+      </c>
+      <c r="C44" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="D44" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="E44" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="F44" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="I44" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="45" spans="1:14" ht="18">
+      <c r="A45" s="2">
+        <v>44</v>
+      </c>
+      <c r="B45" t="s">
+        <v>209</v>
+      </c>
+      <c r="C45" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="D45" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="E45" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="F45" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="I45" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="46" spans="1:14" ht="18">
+      <c r="A46" s="2">
+        <v>45</v>
+      </c>
+      <c r="B46" t="s">
+        <v>210</v>
+      </c>
+      <c r="C46" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="D46" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="E46" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="F46" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="I46" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="47" spans="1:14" ht="18">
+      <c r="A47" s="2">
+        <v>46</v>
+      </c>
+      <c r="B47" t="s">
+        <v>211</v>
+      </c>
+      <c r="C47" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="D47" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="E47" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="F47" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="I47" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="48" spans="1:14" ht="18">
+      <c r="A48" s="2">
+        <v>47</v>
+      </c>
+      <c r="B48" t="s">
+        <v>212</v>
+      </c>
+      <c r="C48" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="D48" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="E48" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="F48" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="I48" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="49" spans="1:9" ht="18">
+      <c r="A49" s="2">
+        <v>48</v>
+      </c>
+      <c r="B49" t="s">
+        <v>214</v>
+      </c>
+      <c r="C49" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="D49" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="E49" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="F49" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="I49" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="50" spans="1:9" ht="18">
+      <c r="A50" s="2">
+        <v>49</v>
+      </c>
+      <c r="B50" t="s">
+        <v>215</v>
+      </c>
+      <c r="C50" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="D50" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="E50" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="F50" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="I50" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="51" spans="1:9" ht="18">
+      <c r="A51" s="2">
+        <v>50</v>
+      </c>
+      <c r="B51" t="s">
+        <v>216</v>
+      </c>
+      <c r="C51" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="D51" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="E51" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="F51" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="I51" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="52" spans="1:9">
+      <c r="A52">
+        <v>51</v>
+      </c>
+      <c r="B52" t="s">
+        <v>217</v>
+      </c>
+      <c r="C52" t="s">
+        <v>157</v>
+      </c>
+      <c r="D52" t="s">
+        <v>158</v>
+      </c>
+      <c r="E52" t="s">
+        <v>159</v>
+      </c>
+      <c r="F52" t="s">
+        <v>160</v>
+      </c>
+      <c r="I52" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="53" spans="1:9">
+      <c r="A53">
+        <v>52</v>
+      </c>
+      <c r="B53" t="s">
+        <v>218</v>
+      </c>
+      <c r="C53" t="s">
+        <v>157</v>
+      </c>
+      <c r="D53" t="s">
+        <v>158</v>
+      </c>
+      <c r="E53" t="s">
+        <v>159</v>
+      </c>
+      <c r="F53" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="54" spans="1:9">
+      <c r="A54">
+        <v>53</v>
+      </c>
+      <c r="B54" t="s">
+        <v>219</v>
+      </c>
+      <c r="C54" t="s">
+        <v>157</v>
+      </c>
+      <c r="D54" t="s">
+        <v>158</v>
+      </c>
+      <c r="E54" t="s">
+        <v>159</v>
+      </c>
+      <c r="F54" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="55" spans="1:9">
+      <c r="A55">
+        <v>54</v>
+      </c>
+      <c r="B55" t="s">
+        <v>220</v>
+      </c>
+      <c r="C55" t="s">
+        <v>157</v>
+      </c>
+      <c r="D55" t="s">
+        <v>158</v>
+      </c>
+      <c r="E55" t="s">
+        <v>159</v>
+      </c>
+      <c r="F55" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="56" spans="1:9">
+      <c r="A56">
+        <v>55</v>
+      </c>
+      <c r="B56" t="s">
+        <v>221</v>
+      </c>
+      <c r="C56" t="s">
+        <v>157</v>
+      </c>
+      <c r="D56" t="s">
+        <v>158</v>
+      </c>
+      <c r="E56" t="s">
+        <v>159</v>
+      </c>
+      <c r="F56" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="57" spans="1:9">
+      <c r="A57">
+        <v>56</v>
+      </c>
+      <c r="B57" t="s">
+        <v>222</v>
+      </c>
+      <c r="C57" t="s">
+        <v>157</v>
+      </c>
+      <c r="D57" t="s">
+        <v>158</v>
+      </c>
+      <c r="E57" t="s">
+        <v>159</v>
+      </c>
+      <c r="F57" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="58" spans="1:9">
+      <c r="A58">
+        <v>57</v>
+      </c>
+      <c r="B58" t="s">
+        <v>223</v>
+      </c>
+      <c r="C58" t="s">
+        <v>157</v>
+      </c>
+      <c r="D58" t="s">
+        <v>158</v>
+      </c>
+      <c r="E58" t="s">
+        <v>159</v>
+      </c>
+      <c r="F58" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="59" spans="1:9">
+      <c r="A59">
+        <v>58</v>
+      </c>
+      <c r="B59" t="s">
+        <v>224</v>
+      </c>
+      <c r="C59" t="s">
+        <v>157</v>
+      </c>
+      <c r="D59" t="s">
+        <v>158</v>
+      </c>
+      <c r="E59" t="s">
+        <v>159</v>
+      </c>
+      <c r="F59" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="60" spans="1:9">
+      <c r="A60">
+        <v>59</v>
+      </c>
+      <c r="B60" t="s">
+        <v>225</v>
+      </c>
+      <c r="C60" t="s">
+        <v>157</v>
+      </c>
+      <c r="D60" t="s">
+        <v>158</v>
+      </c>
+      <c r="E60" t="s">
+        <v>159</v>
+      </c>
+      <c r="F60" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="61" spans="1:9">
+      <c r="A61">
+        <v>60</v>
+      </c>
+      <c r="B61" t="s">
+        <v>226</v>
+      </c>
+      <c r="C61" t="s">
+        <v>157</v>
+      </c>
+      <c r="D61" t="s">
+        <v>158</v>
+      </c>
+      <c r="E61" t="s">
+        <v>159</v>
+      </c>
+      <c r="F61" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="62" spans="1:9">
+      <c r="A62">
+        <v>61</v>
+      </c>
+      <c r="B62" t="s">
+        <v>227</v>
+      </c>
+      <c r="C62" t="s">
+        <v>164</v>
+      </c>
+      <c r="D62" t="s">
+        <v>165</v>
+      </c>
+      <c r="E62" t="s">
+        <v>166</v>
+      </c>
+      <c r="F62" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="63" spans="1:9">
+      <c r="A63">
+        <v>62</v>
+      </c>
+      <c r="B63" t="s">
+        <v>228</v>
+      </c>
+      <c r="C63" t="s">
+        <v>164</v>
+      </c>
+      <c r="D63" t="s">
+        <v>165</v>
+      </c>
+      <c r="E63" t="s">
+        <v>166</v>
+      </c>
+      <c r="F63" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="64" spans="1:9">
+      <c r="A64">
+        <v>63</v>
+      </c>
+      <c r="B64" t="s">
+        <v>229</v>
+      </c>
+      <c r="C64" t="s">
+        <v>164</v>
+      </c>
+      <c r="D64" t="s">
+        <v>165</v>
+      </c>
+      <c r="E64" t="s">
+        <v>166</v>
+      </c>
+      <c r="F64" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="65" spans="1:6">
+      <c r="A65">
+        <v>64</v>
+      </c>
+      <c r="B65" t="s">
+        <v>230</v>
+      </c>
+      <c r="C65" t="s">
+        <v>164</v>
+      </c>
+      <c r="D65" t="s">
+        <v>165</v>
+      </c>
+      <c r="E65" t="s">
+        <v>166</v>
+      </c>
+      <c r="F65" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="66" spans="1:6">
+      <c r="A66">
+        <v>65</v>
+      </c>
+      <c r="B66" t="s">
+        <v>231</v>
+      </c>
+      <c r="C66" t="s">
+        <v>164</v>
+      </c>
+      <c r="D66" t="s">
+        <v>165</v>
+      </c>
+      <c r="E66" t="s">
+        <v>166</v>
+      </c>
+      <c r="F66" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="67" spans="1:6">
+      <c r="A67">
+        <v>66</v>
+      </c>
+      <c r="B67" t="s">
+        <v>232</v>
+      </c>
+      <c r="C67" t="s">
+        <v>164</v>
+      </c>
+      <c r="D67" t="s">
+        <v>165</v>
+      </c>
+      <c r="E67" t="s">
+        <v>166</v>
+      </c>
+      <c r="F67" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="68" spans="1:6">
+      <c r="A68">
+        <v>67</v>
+      </c>
+      <c r="B68" t="s">
+        <v>233</v>
+      </c>
+      <c r="C68" t="s">
+        <v>164</v>
+      </c>
+      <c r="D68" t="s">
+        <v>165</v>
+      </c>
+      <c r="E68" t="s">
+        <v>166</v>
+      </c>
+      <c r="F68" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="69" spans="1:6">
+      <c r="A69">
+        <v>68</v>
+      </c>
+      <c r="B69" t="s">
+        <v>234</v>
+      </c>
+      <c r="C69" t="s">
+        <v>164</v>
+      </c>
+      <c r="D69" t="s">
+        <v>165</v>
+      </c>
+      <c r="E69" t="s">
+        <v>166</v>
+      </c>
+      <c r="F69" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="70" spans="1:6">
+      <c r="A70">
+        <v>69</v>
+      </c>
+      <c r="B70" t="s">
+        <v>235</v>
+      </c>
+      <c r="C70" t="s">
+        <v>164</v>
+      </c>
+      <c r="D70" t="s">
+        <v>165</v>
+      </c>
+      <c r="E70" t="s">
+        <v>166</v>
+      </c>
+      <c r="F70" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="71" spans="1:6">
+      <c r="A71">
+        <v>70</v>
+      </c>
+      <c r="B71" t="s">
+        <v>236</v>
+      </c>
+      <c r="C71" t="s">
+        <v>164</v>
+      </c>
+      <c r="D71" t="s">
+        <v>165</v>
+      </c>
+      <c r="E71" t="s">
+        <v>166</v>
+      </c>
+      <c r="F71" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="72" spans="1:6">
+      <c r="A72">
+        <v>71</v>
+      </c>
+      <c r="B72" t="s">
+        <v>237</v>
+      </c>
+      <c r="C72" t="s">
+        <v>164</v>
+      </c>
+      <c r="D72" t="s">
+        <v>165</v>
+      </c>
+      <c r="E72" t="s">
+        <v>166</v>
+      </c>
+      <c r="F72" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="73" spans="1:6">
+      <c r="A73">
+        <v>72</v>
+      </c>
+      <c r="B73" t="s">
+        <v>238</v>
+      </c>
+      <c r="C73" t="s">
+        <v>164</v>
+      </c>
+      <c r="D73" t="s">
+        <v>165</v>
+      </c>
+      <c r="E73" t="s">
+        <v>166</v>
+      </c>
+      <c r="F73" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="74" spans="1:6">
+      <c r="A74">
+        <v>73</v>
+      </c>
+      <c r="B74" t="s">
+        <v>239</v>
+      </c>
+      <c r="C74" t="s">
+        <v>164</v>
+      </c>
+      <c r="D74" t="s">
+        <v>165</v>
+      </c>
+      <c r="E74" t="s">
+        <v>166</v>
+      </c>
+      <c r="F74" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="75" spans="1:6">
+      <c r="A75">
+        <v>74</v>
+      </c>
+      <c r="B75" t="s">
+        <v>240</v>
+      </c>
+      <c r="C75" t="s">
+        <v>164</v>
+      </c>
+      <c r="D75" t="s">
+        <v>165</v>
+      </c>
+      <c r="E75" t="s">
+        <v>166</v>
+      </c>
+      <c r="F75" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="76" spans="1:6">
+      <c r="A76">
+        <v>75</v>
+      </c>
+      <c r="B76" t="s">
+        <v>241</v>
+      </c>
+      <c r="C76" t="s">
+        <v>164</v>
+      </c>
+      <c r="D76" t="s">
+        <v>165</v>
+      </c>
+      <c r="E76" t="s">
+        <v>166</v>
+      </c>
+      <c r="F76" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="77" spans="1:6">
+      <c r="A77">
+        <v>76</v>
+      </c>
+      <c r="B77" t="s">
+        <v>242</v>
+      </c>
+      <c r="C77" t="s">
+        <v>13</v>
+      </c>
+      <c r="D77" t="s">
+        <v>159</v>
+      </c>
+      <c r="E77" t="s">
+        <v>171</v>
+      </c>
+      <c r="F77" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="78" spans="1:6">
+      <c r="A78">
+        <v>77</v>
+      </c>
+      <c r="B78" t="s">
+        <v>243</v>
+      </c>
+      <c r="C78" t="s">
+        <v>13</v>
+      </c>
+      <c r="D78" t="s">
+        <v>159</v>
+      </c>
+      <c r="E78" t="s">
+        <v>171</v>
+      </c>
+      <c r="F78" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="79" spans="1:6">
+      <c r="A79">
+        <v>78</v>
+      </c>
+      <c r="B79" t="s">
+        <v>244</v>
+      </c>
+      <c r="C79" t="s">
+        <v>13</v>
+      </c>
+      <c r="D79" t="s">
+        <v>159</v>
+      </c>
+      <c r="E79" t="s">
+        <v>171</v>
+      </c>
+      <c r="F79" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="80" spans="1:6">
+      <c r="A80">
+        <v>79</v>
+      </c>
+      <c r="B80" t="s">
+        <v>245</v>
+      </c>
+      <c r="C80" t="s">
+        <v>13</v>
+      </c>
+      <c r="D80" t="s">
+        <v>159</v>
+      </c>
+      <c r="E80" t="s">
+        <v>171</v>
+      </c>
+      <c r="F80" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="81" spans="1:6">
+      <c r="A81">
+        <v>80</v>
+      </c>
+      <c r="B81" t="s">
+        <v>246</v>
+      </c>
+      <c r="C81" t="s">
+        <v>13</v>
+      </c>
+      <c r="D81" t="s">
+        <v>159</v>
+      </c>
+      <c r="E81" t="s">
+        <v>171</v>
+      </c>
+      <c r="F81" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="82" spans="1:6">
+      <c r="A82">
+        <v>81</v>
+      </c>
+      <c r="B82" t="s">
+        <v>247</v>
+      </c>
+      <c r="C82" t="s">
+        <v>13</v>
+      </c>
+      <c r="D82" t="s">
+        <v>159</v>
+      </c>
+      <c r="E82" t="s">
+        <v>171</v>
+      </c>
+      <c r="F82" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="83" spans="1:6">
+      <c r="A83">
+        <v>82</v>
+      </c>
+      <c r="B83" t="s">
+        <v>248</v>
+      </c>
+      <c r="C83" t="s">
+        <v>13</v>
+      </c>
+      <c r="D83" t="s">
+        <v>159</v>
+      </c>
+      <c r="E83" t="s">
+        <v>171</v>
+      </c>
+      <c r="F83" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="84" spans="1:6">
+      <c r="A84">
+        <v>83</v>
+      </c>
+      <c r="B84" t="s">
+        <v>249</v>
+      </c>
+      <c r="C84" t="s">
+        <v>13</v>
+      </c>
+      <c r="D84" t="s">
+        <v>159</v>
+      </c>
+      <c r="E84" t="s">
+        <v>171</v>
+      </c>
+      <c r="F84" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="85" spans="1:6">
+      <c r="A85">
+        <v>84</v>
+      </c>
+      <c r="B85" t="s">
+        <v>250</v>
+      </c>
+      <c r="C85" t="s">
+        <v>13</v>
+      </c>
+      <c r="D85" t="s">
+        <v>159</v>
+      </c>
+      <c r="E85" t="s">
+        <v>171</v>
+      </c>
+      <c r="F85" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="86" spans="1:6">
+      <c r="A86">
+        <v>85</v>
+      </c>
+      <c r="B86" t="s">
+        <v>251</v>
+      </c>
+      <c r="C86" t="s">
+        <v>13</v>
+      </c>
+      <c r="D86" t="s">
+        <v>159</v>
+      </c>
+      <c r="E86" t="s">
+        <v>171</v>
+      </c>
+      <c r="F86" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="87" spans="1:6">
+      <c r="A87">
+        <v>86</v>
+      </c>
+      <c r="B87" t="s">
+        <v>252</v>
+      </c>
+      <c r="C87" t="s">
+        <v>13</v>
+      </c>
+      <c r="D87" t="s">
+        <v>159</v>
+      </c>
+      <c r="E87" t="s">
+        <v>171</v>
+      </c>
+      <c r="F87" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="88" spans="1:6">
+      <c r="A88">
+        <v>87</v>
+      </c>
+      <c r="B88" t="s">
+        <v>253</v>
+      </c>
+      <c r="C88" t="s">
+        <v>13</v>
+      </c>
+      <c r="D88" t="s">
+        <v>159</v>
+      </c>
+      <c r="E88" t="s">
+        <v>171</v>
+      </c>
+      <c r="F88" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="89" spans="1:6">
+      <c r="A89">
+        <v>88</v>
+      </c>
+      <c r="B89" t="s">
+        <v>254</v>
+      </c>
+      <c r="C89" t="s">
+        <v>13</v>
+      </c>
+      <c r="D89" t="s">
+        <v>159</v>
+      </c>
+      <c r="E89" t="s">
+        <v>171</v>
+      </c>
+      <c r="F89" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="90" spans="1:6">
+      <c r="A90">
+        <v>89</v>
+      </c>
+      <c r="B90" t="s">
+        <v>255</v>
+      </c>
+      <c r="C90" t="s">
+        <v>13</v>
+      </c>
+      <c r="D90" t="s">
+        <v>159</v>
+      </c>
+      <c r="E90" t="s">
+        <v>171</v>
+      </c>
+      <c r="F90" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="91" spans="1:6">
+      <c r="A91">
+        <v>90</v>
+      </c>
+      <c r="B91" t="s">
+        <v>256</v>
+      </c>
+      <c r="C91" t="s">
+        <v>13</v>
+      </c>
+      <c r="D91" t="s">
+        <v>159</v>
+      </c>
+      <c r="E91" t="s">
+        <v>171</v>
+      </c>
+      <c r="F91" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="92" spans="1:6">
+      <c r="A92">
+        <v>91</v>
+      </c>
+      <c r="B92" t="s">
+        <v>257</v>
+      </c>
+      <c r="C92" t="s">
+        <v>175</v>
+      </c>
+      <c r="D92" t="s">
+        <v>176</v>
+      </c>
+      <c r="E92" t="s">
+        <v>177</v>
+      </c>
+      <c r="F92" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="93" spans="1:6">
+      <c r="A93">
+        <v>92</v>
+      </c>
+      <c r="B93" t="s">
+        <v>258</v>
+      </c>
+      <c r="C93" t="s">
+        <v>175</v>
+      </c>
+      <c r="D93" t="s">
+        <v>176</v>
+      </c>
+      <c r="E93" t="s">
+        <v>177</v>
+      </c>
+      <c r="F93" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="94" spans="1:6">
+      <c r="A94">
+        <v>93</v>
+      </c>
+      <c r="B94" t="s">
+        <v>259</v>
+      </c>
+      <c r="C94" t="s">
+        <v>175</v>
+      </c>
+      <c r="D94" t="s">
+        <v>176</v>
+      </c>
+      <c r="E94" t="s">
+        <v>177</v>
+      </c>
+      <c r="F94" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="95" spans="1:6">
+      <c r="A95">
+        <v>94</v>
+      </c>
+      <c r="B95" t="s">
+        <v>260</v>
+      </c>
+      <c r="C95" t="s">
+        <v>175</v>
+      </c>
+      <c r="D95" t="s">
+        <v>176</v>
+      </c>
+      <c r="E95" t="s">
+        <v>177</v>
+      </c>
+      <c r="F95" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="96" spans="1:6">
+      <c r="A96">
+        <v>95</v>
+      </c>
+      <c r="B96" t="s">
+        <v>261</v>
+      </c>
+      <c r="C96" t="s">
+        <v>175</v>
+      </c>
+      <c r="D96" t="s">
+        <v>176</v>
+      </c>
+      <c r="E96" t="s">
+        <v>177</v>
+      </c>
+      <c r="F96" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="97" spans="1:6">
+      <c r="A97">
+        <v>96</v>
+      </c>
+      <c r="B97" t="s">
+        <v>262</v>
+      </c>
+      <c r="C97" t="s">
+        <v>175</v>
+      </c>
+      <c r="D97" t="s">
+        <v>176</v>
+      </c>
+      <c r="E97" t="s">
+        <v>177</v>
+      </c>
+      <c r="F97" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="98" spans="1:6">
+      <c r="A98">
+        <v>97</v>
+      </c>
+      <c r="B98" t="s">
+        <v>263</v>
+      </c>
+      <c r="C98" t="s">
+        <v>175</v>
+      </c>
+      <c r="D98" t="s">
+        <v>176</v>
+      </c>
+      <c r="E98" t="s">
+        <v>177</v>
+      </c>
+      <c r="F98" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="99" spans="1:6">
+      <c r="A99">
+        <v>98</v>
+      </c>
+      <c r="B99" t="s">
+        <v>264</v>
+      </c>
+      <c r="C99" t="s">
+        <v>175</v>
+      </c>
+      <c r="D99" t="s">
+        <v>176</v>
+      </c>
+      <c r="E99" t="s">
+        <v>177</v>
+      </c>
+      <c r="F99" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="100" spans="1:6">
+      <c r="A100">
+        <v>99</v>
+      </c>
+      <c r="B100" t="s">
+        <v>265</v>
+      </c>
+      <c r="C100" t="s">
+        <v>175</v>
+      </c>
+      <c r="D100" t="s">
+        <v>176</v>
+      </c>
+      <c r="E100" t="s">
+        <v>177</v>
+      </c>
+      <c r="F100" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="101" spans="1:6">
+      <c r="A101">
+        <v>100</v>
+      </c>
+      <c r="B101" t="s">
+        <v>266</v>
+      </c>
+      <c r="C101" t="s">
+        <v>175</v>
+      </c>
+      <c r="D101" t="s">
+        <v>176</v>
+      </c>
+      <c r="E101" t="s">
+        <v>177</v>
+      </c>
+      <c r="F101" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="102" spans="1:6">
+      <c r="A102">
+        <v>101</v>
+      </c>
+      <c r="B102" t="s">
+        <v>267</v>
+      </c>
+      <c r="C102" t="s">
+        <v>175</v>
+      </c>
+      <c r="D102" t="s">
+        <v>176</v>
+      </c>
+      <c r="E102" t="s">
+        <v>177</v>
+      </c>
+      <c r="F102" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="103" spans="1:6">
+      <c r="A103">
+        <v>102</v>
+      </c>
+      <c r="B103" t="s">
+        <v>268</v>
+      </c>
+      <c r="C103" t="s">
+        <v>175</v>
+      </c>
+      <c r="D103" t="s">
+        <v>176</v>
+      </c>
+      <c r="E103" t="s">
+        <v>177</v>
+      </c>
+      <c r="F103" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="104" spans="1:6">
+      <c r="A104">
+        <v>103</v>
+      </c>
+      <c r="B104" t="s">
+        <v>269</v>
+      </c>
+      <c r="C104" t="s">
+        <v>175</v>
+      </c>
+      <c r="D104" t="s">
+        <v>176</v>
+      </c>
+      <c r="E104" t="s">
+        <v>177</v>
+      </c>
+      <c r="F104" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="105" spans="1:6">
+      <c r="A105">
+        <v>104</v>
+      </c>
+      <c r="B105" t="s">
+        <v>270</v>
+      </c>
+      <c r="C105" t="s">
+        <v>175</v>
+      </c>
+      <c r="D105" t="s">
+        <v>176</v>
+      </c>
+      <c r="E105" t="s">
+        <v>177</v>
+      </c>
+      <c r="F105" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="106" spans="1:6">
+      <c r="A106">
+        <v>105</v>
+      </c>
+      <c r="B106" t="s">
+        <v>271</v>
+      </c>
+      <c r="C106" t="s">
+        <v>175</v>
+      </c>
+      <c r="D106" t="s">
+        <v>176</v>
+      </c>
+      <c r="E106" t="s">
+        <v>177</v>
+      </c>
+      <c r="F106" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="107" spans="1:6">
+      <c r="A107">
+        <v>106</v>
+      </c>
+      <c r="B107" t="s">
+        <v>272</v>
+      </c>
+      <c r="C107" t="s">
+        <v>175</v>
+      </c>
+      <c r="D107" t="s">
+        <v>176</v>
+      </c>
+      <c r="E107" t="s">
+        <v>177</v>
+      </c>
+      <c r="F107" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="108" spans="1:6">
+      <c r="A108">
+        <v>107</v>
+      </c>
+      <c r="B108" t="s">
+        <v>273</v>
+      </c>
+      <c r="C108" t="s">
+        <v>175</v>
+      </c>
+      <c r="D108" t="s">
+        <v>176</v>
+      </c>
+      <c r="E108" t="s">
+        <v>177</v>
+      </c>
+      <c r="F108" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="109" spans="1:6">
+      <c r="A109">
+        <v>108</v>
+      </c>
+      <c r="B109" t="s">
+        <v>274</v>
+      </c>
+      <c r="C109" t="s">
+        <v>175</v>
+      </c>
+      <c r="D109" t="s">
+        <v>176</v>
+      </c>
+      <c r="E109" t="s">
+        <v>177</v>
+      </c>
+      <c r="F109" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="110" spans="1:6">
+      <c r="A110">
+        <v>109</v>
+      </c>
+      <c r="B110" t="s">
+        <v>275</v>
+      </c>
+      <c r="C110" t="s">
+        <v>175</v>
+      </c>
+      <c r="D110" t="s">
+        <v>176</v>
+      </c>
+      <c r="E110" t="s">
+        <v>177</v>
+      </c>
+      <c r="F110" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="111" spans="1:6">
+      <c r="A111">
+        <v>110</v>
+      </c>
+      <c r="B111" t="s">
+        <v>276</v>
+      </c>
+      <c r="C111" t="s">
+        <v>175</v>
+      </c>
+      <c r="D111" t="s">
+        <v>176</v>
+      </c>
+      <c r="E111" t="s">
+        <v>177</v>
+      </c>
+      <c r="F111" t="s">
+        <v>178</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:F111" xr:uid="{CB2143CE-4BEA-1F43-9B14-FF0CEB6C4E85}"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CE1B5BBB-6199-DD40-84BD-D3DEFF05FD8A}">
+  <dimension ref="E4:G7"/>
+  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.95"/>
+  <sheetData>
+    <row r="4" spans="5:7">
+      <c r="F4" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="5" spans="5:7">
+      <c r="E5" t="s">
+        <v>278</v>
+      </c>
+      <c r="G5" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="7" spans="5:7">
+      <c r="F7" t="s">
+        <v>280</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FF2A96F8-74E3-45A2-AD2F-99E4606A4139}">
+  <dimension ref="A1:O111"/>
+  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.95"/>
+  <cols>
+    <col min="2" max="2" width="24.875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="16.625" customWidth="1"/>
+    <col min="7" max="7" width="15.375" customWidth="1"/>
+    <col min="8" max="8" width="22.375" customWidth="1"/>
+    <col min="9" max="9" width="11.875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="21.5" customWidth="1"/>
+    <col min="11" max="11" width="26.875" customWidth="1"/>
+    <col min="12" max="12" width="11.375" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="20.875" customWidth="1"/>
+    <col min="14" max="14" width="11.375" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="11" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:15" ht="18">
+      <c r="A1" s="4" t="s">
+        <v>110</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="4" t="s">
+        <v>111</v>
+      </c>
+      <c r="D1" s="4" t="s">
+        <v>112</v>
+      </c>
+      <c r="E1" s="4" t="s">
+        <v>113</v>
+      </c>
+      <c r="F1" s="4" t="s">
+        <v>114</v>
+      </c>
+      <c r="G1" s="4" t="s">
+        <v>281</v>
+      </c>
+      <c r="H1" s="4" t="s">
+        <v>282</v>
+      </c>
+      <c r="I1" s="4" t="s">
+        <v>283</v>
+      </c>
+      <c r="J1" s="4" t="s">
+        <v>284</v>
+      </c>
+      <c r="K1" s="4" t="s">
+        <v>285</v>
+      </c>
+      <c r="L1" s="4" t="s">
+        <v>286</v>
+      </c>
+      <c r="M1" s="4" t="s">
+        <v>287</v>
+      </c>
+      <c r="N1" s="4" t="s">
+        <v>288</v>
+      </c>
+      <c r="O1" s="4"/>
+    </row>
+    <row r="2" spans="1:15" ht="18">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D2">
+        <v>0.57999999999999996</v>
+      </c>
+      <c r="E2">
+        <v>0.38</v>
+      </c>
+      <c r="F2" t="s">
+        <v>115</v>
+      </c>
+      <c r="G2">
+        <v>152327635</v>
+      </c>
+      <c r="H2">
+        <v>105530260</v>
+      </c>
+      <c r="I2">
+        <v>0.1</v>
+      </c>
+      <c r="J2">
+        <v>0.03</v>
+      </c>
+      <c r="K2">
+        <v>20000</v>
+      </c>
+      <c r="L2">
+        <v>0.8</v>
+      </c>
+      <c r="M2">
+        <v>0.95</v>
+      </c>
+      <c r="N2" s="2">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:15" ht="18">
+      <c r="A3">
+        <v>2</v>
+      </c>
+      <c r="B3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D3">
+        <v>0.65</v>
+      </c>
+      <c r="E3">
+        <v>0.45</v>
+      </c>
+      <c r="F3" t="s">
+        <v>116</v>
+      </c>
+      <c r="G3">
+        <v>107548575</v>
+      </c>
+      <c r="H3">
+        <v>86261449</v>
+      </c>
+      <c r="I3">
+        <v>0.08</v>
+      </c>
+      <c r="J3">
+        <v>2.5000000000000001E-2</v>
+      </c>
+      <c r="K3">
+        <v>18000</v>
+      </c>
+      <c r="L3">
+        <v>0.78</v>
+      </c>
+      <c r="M3">
+        <v>0.95</v>
+      </c>
+      <c r="N3" s="2">
+        <v>0.19</v>
+      </c>
+      <c r="O3" s="2"/>
+    </row>
+    <row r="4" spans="1:15" ht="18">
+      <c r="A4">
+        <v>3</v>
+      </c>
+      <c r="B4" t="s">
+        <v>12</v>
+      </c>
+      <c r="C4" t="s">
+        <v>13</v>
+      </c>
+      <c r="D4">
+        <v>0.68</v>
+      </c>
+      <c r="E4">
+        <v>0.57999999999999996</v>
+      </c>
+      <c r="F4" t="s">
+        <v>117</v>
+      </c>
+      <c r="G4">
+        <v>118962840</v>
+      </c>
+      <c r="H4">
+        <v>122793833</v>
+      </c>
+      <c r="I4">
+        <v>0.09</v>
+      </c>
+      <c r="J4">
+        <v>0.03</v>
+      </c>
+      <c r="K4">
+        <v>22000</v>
+      </c>
+      <c r="L4">
+        <v>0.85</v>
+      </c>
+      <c r="M4">
+        <v>0.97</v>
+      </c>
+      <c r="N4" s="2">
+        <v>0.23</v>
+      </c>
+      <c r="O4" s="2"/>
+    </row>
+    <row r="5" spans="1:15" ht="18">
+      <c r="A5">
+        <v>4</v>
+      </c>
+      <c r="B5" t="s">
+        <v>15</v>
+      </c>
+      <c r="C5" t="s">
+        <v>16</v>
+      </c>
+      <c r="D5">
+        <v>0.72</v>
+      </c>
+      <c r="E5">
+        <v>0.42</v>
+      </c>
+      <c r="F5" t="s">
+        <v>118</v>
+      </c>
+      <c r="G5">
+        <v>118962840</v>
+      </c>
+      <c r="H5">
+        <v>123000000</v>
+      </c>
+      <c r="I5">
+        <v>0.09</v>
+      </c>
+      <c r="J5">
+        <v>0.03</v>
+      </c>
+      <c r="K5">
+        <v>22000</v>
+      </c>
+      <c r="L5">
+        <v>0.85</v>
+      </c>
+      <c r="M5">
+        <v>0.97</v>
+      </c>
+      <c r="N5" s="2">
+        <v>0.23</v>
+      </c>
+      <c r="O5" s="2"/>
+    </row>
+    <row r="6" spans="1:15" ht="18">
+      <c r="A6">
+        <v>5</v>
+      </c>
+      <c r="B6" t="s">
+        <v>18</v>
+      </c>
+      <c r="C6" t="s">
+        <v>19</v>
+      </c>
+      <c r="D6">
+        <v>0.75</v>
+      </c>
+      <c r="E6">
+        <v>0.65</v>
+      </c>
+      <c r="F6" t="s">
+        <v>119</v>
+      </c>
+      <c r="G6">
+        <v>110860174</v>
+      </c>
+      <c r="H6">
+        <v>122000000</v>
+      </c>
+      <c r="I6">
+        <v>0.1</v>
+      </c>
+      <c r="J6">
+        <v>0.04</v>
+      </c>
+      <c r="K6">
+        <v>21000</v>
+      </c>
+      <c r="L6">
+        <v>0.9</v>
+      </c>
+      <c r="M6">
+        <v>0.96</v>
+      </c>
+      <c r="N6" s="2">
+        <v>0.28999999999999998</v>
+      </c>
+      <c r="O6" s="2"/>
+    </row>
+    <row r="7" spans="1:15" ht="18">
+      <c r="A7">
+        <v>6</v>
+      </c>
+      <c r="B7" t="s">
+        <v>21</v>
+      </c>
+      <c r="C7" t="s">
+        <v>22</v>
+      </c>
+      <c r="D7">
+        <v>0.35</v>
+      </c>
+      <c r="E7">
+        <v>0.25</v>
+      </c>
+      <c r="F7" t="s">
+        <v>120</v>
+      </c>
+      <c r="G7">
+        <v>123563025</v>
+      </c>
+      <c r="H7">
+        <v>90067253</v>
+      </c>
+      <c r="I7">
+        <v>0.11</v>
+      </c>
+      <c r="J7">
+        <v>3.5000000000000003E-2</v>
+      </c>
+      <c r="K7">
+        <v>20000</v>
+      </c>
+      <c r="L7">
+        <v>0.88</v>
+      </c>
+      <c r="M7">
+        <v>0.94</v>
+      </c>
+      <c r="N7" s="2">
+        <v>0.27</v>
+      </c>
+      <c r="O7" s="2"/>
+    </row>
+    <row r="8" spans="1:15" ht="18">
+      <c r="A8">
+        <v>7</v>
+      </c>
+      <c r="B8" t="s">
+        <v>24</v>
+      </c>
+      <c r="C8" t="s">
+        <v>25</v>
+      </c>
+      <c r="D8">
+        <v>0.48</v>
+      </c>
+      <c r="E8">
+        <v>0.45</v>
+      </c>
+      <c r="F8" t="s">
+        <v>121</v>
+      </c>
+      <c r="G8">
+        <v>6000000</v>
+      </c>
+      <c r="H8">
+        <v>30000000</v>
+      </c>
+      <c r="I8">
+        <v>0.09</v>
+      </c>
+      <c r="J8">
+        <v>0.08</v>
+      </c>
+      <c r="K8">
+        <v>7000</v>
+      </c>
+      <c r="L8">
+        <v>0.6</v>
+      </c>
+      <c r="M8">
+        <v>0.75</v>
+      </c>
+      <c r="N8" s="2">
+        <v>0.36</v>
+      </c>
+      <c r="O8" s="2"/>
+    </row>
+    <row r="9" spans="1:15" ht="18">
+      <c r="A9">
+        <v>8</v>
+      </c>
+      <c r="B9" t="s">
+        <v>27</v>
+      </c>
+      <c r="C9" t="s">
+        <v>28</v>
+      </c>
+      <c r="D9">
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="E9">
+        <v>0.35</v>
+      </c>
+      <c r="F9" t="s">
+        <v>122</v>
+      </c>
+      <c r="G9">
+        <v>30000000</v>
+      </c>
+      <c r="H9">
+        <v>71540000</v>
+      </c>
+      <c r="I9">
+        <v>0.1</v>
+      </c>
+      <c r="J9">
+        <v>0.05</v>
+      </c>
+      <c r="K9">
+        <v>15000</v>
+      </c>
+      <c r="L9">
+        <v>0.82</v>
+      </c>
+      <c r="M9">
+        <v>0.9</v>
+      </c>
+      <c r="N9" s="2">
+        <v>0.31</v>
+      </c>
+      <c r="O9" s="2"/>
+    </row>
+    <row r="10" spans="1:15" ht="18">
+      <c r="A10">
+        <v>9</v>
+      </c>
+      <c r="B10" t="s">
+        <v>30</v>
+      </c>
+      <c r="C10" t="s">
+        <v>31</v>
+      </c>
+      <c r="D10">
+        <v>0.85</v>
+      </c>
+      <c r="E10">
+        <v>0.22</v>
+      </c>
+      <c r="F10" t="s">
+        <v>123</v>
+      </c>
+      <c r="G10">
+        <v>28000000</v>
+      </c>
+      <c r="H10">
+        <v>65000000</v>
+      </c>
+      <c r="I10">
+        <v>0.09</v>
+      </c>
+      <c r="J10">
+        <v>0.04</v>
+      </c>
+      <c r="K10">
+        <v>16000</v>
+      </c>
+      <c r="L10">
+        <v>0.87</v>
+      </c>
+      <c r="M10">
+        <v>0.92</v>
+      </c>
+      <c r="N10" s="2">
+        <v>0.28999999999999998</v>
+      </c>
+      <c r="O10" s="2"/>
+    </row>
+    <row r="11" spans="1:15" ht="18">
+      <c r="A11">
+        <v>10</v>
+      </c>
+      <c r="B11" t="s">
+        <v>33</v>
+      </c>
+      <c r="C11" t="s">
+        <v>31</v>
+      </c>
+      <c r="D11">
+        <v>0.7</v>
+      </c>
+      <c r="E11">
+        <v>0.48</v>
+      </c>
+      <c r="F11" t="s">
+        <v>124</v>
+      </c>
+      <c r="G11">
+        <v>32000000</v>
+      </c>
+      <c r="H11">
+        <v>73430000</v>
+      </c>
+      <c r="I11">
+        <v>0.08</v>
+      </c>
+      <c r="J11">
+        <v>0.03</v>
+      </c>
+      <c r="K11">
+        <v>14000</v>
+      </c>
+      <c r="L11">
+        <v>0.75</v>
+      </c>
+      <c r="M11">
+        <v>0.95</v>
+      </c>
+      <c r="N11" s="2">
+        <v>0.23</v>
+      </c>
+      <c r="O11" s="2"/>
+    </row>
+    <row r="12" spans="1:15" ht="18">
+      <c r="A12">
+        <v>11</v>
+      </c>
+      <c r="B12" t="s">
+        <v>41</v>
+      </c>
+      <c r="C12" t="s">
+        <v>42</v>
+      </c>
+      <c r="D12">
+        <v>0.74</v>
+      </c>
+      <c r="E12">
+        <v>0.7</v>
+      </c>
+      <c r="F12" t="s">
+        <v>125</v>
+      </c>
+      <c r="G12">
+        <v>25000000</v>
+      </c>
+      <c r="H12">
+        <v>66810000</v>
+      </c>
+      <c r="I12">
+        <v>0.11</v>
+      </c>
+      <c r="J12">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="K12">
+        <v>15000</v>
+      </c>
+      <c r="L12">
+        <v>0.9</v>
+      </c>
+      <c r="M12">
+        <v>0.88</v>
+      </c>
+      <c r="N12" s="2">
+        <v>0.34</v>
+      </c>
+      <c r="O12" s="2"/>
+    </row>
+    <row r="13" spans="1:15" ht="18">
+      <c r="A13">
+        <v>12</v>
+      </c>
+      <c r="B13" t="s">
+        <v>54</v>
+      </c>
+      <c r="C13" t="s">
+        <v>55</v>
+      </c>
+      <c r="D13">
+        <v>0.6</v>
+      </c>
+      <c r="E13">
+        <v>0.35</v>
+      </c>
+      <c r="F13" t="s">
+        <v>126</v>
+      </c>
+      <c r="G13">
+        <v>42000000</v>
+      </c>
+      <c r="H13">
+        <v>62000000</v>
+      </c>
+      <c r="I13">
+        <v>0.1</v>
+      </c>
+      <c r="J13">
+        <v>0.05</v>
+      </c>
+      <c r="K13">
+        <v>16000</v>
+      </c>
+      <c r="L13">
+        <v>0.88</v>
+      </c>
+      <c r="M13">
+        <v>0.9</v>
+      </c>
+      <c r="N13" s="2">
+        <v>0.31</v>
+      </c>
+      <c r="O13" s="2"/>
+    </row>
+    <row r="14" spans="1:15" ht="18">
+      <c r="A14">
+        <v>13</v>
+      </c>
+      <c r="B14" t="s">
+        <v>100</v>
+      </c>
+      <c r="C14" t="s">
+        <v>127</v>
+      </c>
+      <c r="D14">
+        <v>0.72</v>
+      </c>
+      <c r="E14">
+        <v>0.75</v>
+      </c>
+      <c r="F14" t="s">
+        <v>128</v>
+      </c>
+      <c r="G14">
+        <v>18000000</v>
+      </c>
+      <c r="H14">
+        <v>44680000</v>
+      </c>
+      <c r="I14">
+        <v>0.09</v>
+      </c>
+      <c r="J14">
+        <v>0.06</v>
+      </c>
+      <c r="K14">
+        <v>12000</v>
+      </c>
+      <c r="L14">
+        <v>0.85</v>
+      </c>
+      <c r="M14">
+        <v>0.85</v>
+      </c>
+      <c r="N14" s="2">
+        <v>0.32</v>
+      </c>
+      <c r="O14" s="2"/>
+    </row>
+    <row r="15" spans="1:15" ht="18">
+      <c r="A15">
+        <v>14</v>
+      </c>
+      <c r="B15" t="s">
+        <v>35</v>
+      </c>
+      <c r="C15" t="s">
+        <v>42</v>
+      </c>
+      <c r="D15">
+        <v>0.62</v>
+      </c>
+      <c r="E15">
+        <v>0.52</v>
+      </c>
+      <c r="F15" t="s">
+        <v>129</v>
+      </c>
+      <c r="G15">
+        <v>109000000</v>
+      </c>
+      <c r="H15">
+        <v>86600000</v>
+      </c>
+      <c r="I15">
+        <v>0.1</v>
+      </c>
+      <c r="J15">
+        <v>0.03</v>
+      </c>
+      <c r="K15">
+        <v>22000</v>
+      </c>
+      <c r="L15">
+        <v>0.88</v>
+      </c>
+      <c r="M15">
+        <v>0.97</v>
+      </c>
+      <c r="N15" s="2">
+        <v>0.25</v>
+      </c>
+      <c r="O15" s="2"/>
+    </row>
+    <row r="16" spans="1:15" ht="18">
+      <c r="A16">
+        <v>15</v>
+      </c>
+      <c r="B16" t="s">
+        <v>38</v>
+      </c>
+      <c r="C16" t="s">
+        <v>31</v>
+      </c>
+      <c r="D16">
+        <v>0.78</v>
+      </c>
+      <c r="E16">
+        <v>0.32</v>
+      </c>
+      <c r="F16" t="s">
+        <v>130</v>
+      </c>
+      <c r="G16">
+        <v>30000000</v>
+      </c>
+      <c r="H16">
+        <v>55260000</v>
+      </c>
+      <c r="I16">
+        <v>0.08</v>
+      </c>
+      <c r="J16">
+        <v>0.03</v>
+      </c>
+      <c r="K16">
+        <v>15000</v>
+      </c>
+      <c r="L16">
+        <v>0.75</v>
+      </c>
+      <c r="M16">
+        <v>0.9</v>
+      </c>
+      <c r="N16" s="2">
+        <v>0.23</v>
+      </c>
+      <c r="O16" s="2"/>
+    </row>
+    <row r="17" spans="1:15" ht="18">
+      <c r="A17">
+        <v>16</v>
+      </c>
+      <c r="B17" t="s">
+        <v>51</v>
+      </c>
+      <c r="C17" t="s">
+        <v>52</v>
+      </c>
+      <c r="D17">
+        <v>0.82</v>
+      </c>
+      <c r="E17">
+        <v>0.78</v>
+      </c>
+      <c r="F17" t="s">
+        <v>131</v>
+      </c>
+      <c r="G17">
+        <v>75000000</v>
+      </c>
+      <c r="H17">
+        <v>66030000</v>
+      </c>
+      <c r="I17">
+        <v>0.09</v>
+      </c>
+      <c r="J17">
+        <v>3.5000000000000003E-2</v>
+      </c>
+      <c r="K17">
+        <v>18000</v>
+      </c>
+      <c r="L17">
+        <v>0.85</v>
+      </c>
+      <c r="M17">
+        <v>0.93</v>
+      </c>
+      <c r="N17" s="2">
+        <v>0.26</v>
+      </c>
+      <c r="O17" s="2"/>
+    </row>
+    <row r="18" spans="1:15" ht="18">
+      <c r="A18">
+        <v>17</v>
+      </c>
+      <c r="B18" t="s">
+        <v>48</v>
+      </c>
+      <c r="C18" t="s">
+        <v>73</v>
+      </c>
+      <c r="D18">
+        <v>0.65</v>
+      </c>
+      <c r="E18">
+        <v>0.5</v>
+      </c>
+      <c r="F18" t="s">
+        <v>132</v>
+      </c>
+      <c r="G18">
+        <v>65000000</v>
+      </c>
+      <c r="H18">
+        <v>64220000</v>
+      </c>
+      <c r="I18">
+        <v>0.09</v>
+      </c>
+      <c r="J18">
+        <v>0.03</v>
+      </c>
+      <c r="K18">
+        <v>17000</v>
+      </c>
+      <c r="L18">
+        <v>0.82</v>
+      </c>
+      <c r="M18">
+        <v>0.92</v>
+      </c>
+      <c r="N18" s="2">
+        <v>0.25</v>
+      </c>
+      <c r="O18" s="2"/>
+    </row>
+    <row r="19" spans="1:15" ht="18">
+      <c r="A19">
+        <v>18</v>
+      </c>
+      <c r="B19" t="s">
+        <v>44</v>
+      </c>
+      <c r="C19" t="s">
+        <v>13</v>
+      </c>
+      <c r="D19">
+        <v>0.72</v>
+      </c>
+      <c r="E19">
+        <v>0.6</v>
+      </c>
+      <c r="F19" t="s">
+        <v>133</v>
+      </c>
+      <c r="G19">
+        <v>9000000</v>
+      </c>
+      <c r="H19">
+        <v>40000000</v>
+      </c>
+      <c r="I19">
+        <v>0.08</v>
+      </c>
+      <c r="J19">
+        <v>0.05</v>
+      </c>
+      <c r="K19">
+        <v>9000</v>
+      </c>
+      <c r="L19">
+        <v>0.7</v>
+      </c>
+      <c r="M19">
+        <v>0.85</v>
+      </c>
+      <c r="N19" s="2">
+        <v>0.28999999999999998</v>
+      </c>
+      <c r="O19" s="2"/>
+    </row>
+    <row r="20" spans="1:15" ht="18">
+      <c r="A20">
+        <v>19</v>
+      </c>
+      <c r="B20" t="s">
+        <v>69</v>
+      </c>
+      <c r="C20" t="s">
+        <v>70</v>
+      </c>
+      <c r="D20">
+        <v>0.72</v>
+      </c>
+      <c r="E20">
+        <v>0.68</v>
+      </c>
+      <c r="F20" t="s">
+        <v>134</v>
+      </c>
+      <c r="G20">
+        <v>50000000</v>
+      </c>
+      <c r="H20">
+        <v>57370000</v>
+      </c>
+      <c r="I20">
+        <v>0.1</v>
+      </c>
+      <c r="J20">
+        <v>0.04</v>
+      </c>
+      <c r="K20">
+        <v>16000</v>
+      </c>
+      <c r="L20">
+        <v>0.9</v>
+      </c>
+      <c r="M20">
+        <v>0.9</v>
+      </c>
+      <c r="N20" s="2">
+        <v>0.28999999999999998</v>
+      </c>
+      <c r="O20" s="2"/>
+    </row>
+    <row r="21" spans="1:15" ht="18">
+      <c r="A21">
+        <v>20</v>
+      </c>
+      <c r="B21" t="s">
+        <v>72</v>
+      </c>
+      <c r="C21" t="s">
+        <v>73</v>
+      </c>
+      <c r="D21">
+        <v>0.64</v>
+      </c>
+      <c r="E21">
+        <v>0.57999999999999996</v>
+      </c>
+      <c r="F21" t="s">
+        <v>135</v>
+      </c>
+      <c r="G21">
+        <v>60000000</v>
+      </c>
+      <c r="H21">
+        <v>60610000</v>
+      </c>
+      <c r="I21">
+        <v>0.09</v>
+      </c>
+      <c r="J21">
+        <v>0.03</v>
+      </c>
+      <c r="K21">
+        <v>17000</v>
+      </c>
+      <c r="L21">
+        <v>0.8</v>
+      </c>
+      <c r="M21">
+        <v>0.94</v>
+      </c>
+      <c r="N21" s="2">
+        <v>0.25</v>
+      </c>
+      <c r="O21" s="2"/>
+    </row>
+    <row r="22" spans="1:15" ht="18">
+      <c r="A22">
+        <v>21</v>
+      </c>
+      <c r="B22" t="s">
+        <v>95</v>
+      </c>
+      <c r="C22" t="s">
+        <v>96</v>
+      </c>
+      <c r="D22">
+        <v>0.45</v>
+      </c>
+      <c r="E22">
+        <v>0.38</v>
+      </c>
+      <c r="F22" t="s">
+        <v>128</v>
+      </c>
+      <c r="G22">
+        <v>8000000</v>
+      </c>
+      <c r="H22">
+        <v>30000000</v>
+      </c>
+      <c r="I22">
+        <v>0.09</v>
+      </c>
+      <c r="J22">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="K22">
+        <v>8000</v>
+      </c>
+      <c r="L22">
+        <v>0.75</v>
+      </c>
+      <c r="M22">
+        <v>0.8</v>
+      </c>
+      <c r="N22" s="2">
+        <v>0.33</v>
+      </c>
+      <c r="O22" s="2"/>
+    </row>
+    <row r="23" spans="1:15" ht="18">
+      <c r="A23">
+        <v>22</v>
+      </c>
+      <c r="B23" t="s">
+        <v>136</v>
+      </c>
+      <c r="C23" t="s">
+        <v>137</v>
+      </c>
+      <c r="D23">
+        <v>0.65</v>
+      </c>
+      <c r="E23">
+        <v>0.4</v>
+      </c>
+      <c r="F23" t="s">
+        <v>128</v>
+      </c>
+      <c r="G23">
+        <v>7000000</v>
+      </c>
+      <c r="H23">
+        <v>25000000</v>
+      </c>
+      <c r="I23">
+        <v>0.11</v>
+      </c>
+      <c r="J23">
+        <v>0.08</v>
+      </c>
+      <c r="K23">
+        <v>9000</v>
+      </c>
+      <c r="L23">
+        <v>0.92</v>
+      </c>
+      <c r="M23">
+        <v>0.78</v>
+      </c>
+      <c r="N23" s="2">
+        <v>0.36</v>
+      </c>
+      <c r="O23" s="2"/>
+    </row>
+    <row r="24" spans="1:15" ht="18">
+      <c r="A24">
+        <v>23</v>
+      </c>
+      <c r="B24" t="s">
+        <v>103</v>
+      </c>
+      <c r="C24" t="s">
+        <v>42</v>
+      </c>
+      <c r="D24">
+        <v>0.75</v>
+      </c>
+      <c r="E24">
+        <v>0.68</v>
+      </c>
+      <c r="F24" t="s">
+        <v>125</v>
+      </c>
+      <c r="G24">
+        <v>6000000</v>
+      </c>
+      <c r="H24">
+        <v>28000000</v>
+      </c>
+      <c r="I24">
+        <v>0.12</v>
+      </c>
+      <c r="J24">
+        <v>0.09</v>
+      </c>
+      <c r="K24">
+        <v>8500</v>
+      </c>
+      <c r="L24">
+        <v>0.95</v>
+      </c>
+      <c r="M24">
+        <v>0.78</v>
+      </c>
+      <c r="N24" s="2">
+        <v>0.39</v>
+      </c>
+      <c r="O24" s="2"/>
+    </row>
+    <row r="25" spans="1:15" ht="18">
+      <c r="A25">
+        <v>24</v>
+      </c>
+      <c r="B25" t="s">
+        <v>57</v>
+      </c>
+      <c r="C25" t="s">
+        <v>31</v>
+      </c>
+      <c r="D25">
+        <v>0.76</v>
+      </c>
+      <c r="E25">
+        <v>0.28000000000000003</v>
+      </c>
+      <c r="F25" t="s">
+        <v>138</v>
+      </c>
+      <c r="G25">
+        <v>12000000</v>
+      </c>
+      <c r="H25">
+        <v>43460000</v>
+      </c>
+      <c r="I25">
+        <v>0.08</v>
+      </c>
+      <c r="J25">
+        <v>0.04</v>
+      </c>
+      <c r="K25">
+        <v>13000</v>
+      </c>
+      <c r="L25">
+        <v>0.78</v>
+      </c>
+      <c r="M25">
+        <v>0.88</v>
+      </c>
+      <c r="N25" s="2">
+        <v>0.26</v>
+      </c>
+      <c r="O25" s="2"/>
+    </row>
+    <row r="26" spans="1:15" ht="18">
+      <c r="A26">
+        <v>25</v>
+      </c>
+      <c r="B26" t="s">
+        <v>61</v>
+      </c>
+      <c r="C26" t="s">
+        <v>62</v>
+      </c>
+      <c r="D26">
+        <v>0.3</v>
+      </c>
+      <c r="E26">
+        <v>0.2</v>
+      </c>
+      <c r="F26" t="s">
+        <v>139</v>
+      </c>
+      <c r="G26">
+        <v>55000000</v>
+      </c>
+      <c r="H26">
+        <v>66520000</v>
+      </c>
+      <c r="I26">
+        <v>0.09</v>
+      </c>
+      <c r="J26">
+        <v>0.03</v>
+      </c>
+      <c r="K26">
+        <v>18000</v>
+      </c>
+      <c r="L26">
+        <v>0.8</v>
+      </c>
+      <c r="M26">
+        <v>0.93</v>
+      </c>
+      <c r="N26" s="2">
+        <v>0.25</v>
+      </c>
+      <c r="O26" s="2"/>
+    </row>
+    <row r="27" spans="1:15" ht="18">
+      <c r="A27">
+        <v>26</v>
+      </c>
+      <c r="B27" t="s">
+        <v>64</v>
+      </c>
+      <c r="C27" t="s">
+        <v>42</v>
+      </c>
+      <c r="D27">
+        <v>0.65</v>
+      </c>
+      <c r="E27">
+        <v>0.62</v>
+      </c>
+      <c r="F27" t="s">
+        <v>140</v>
+      </c>
+      <c r="G27">
+        <v>87000000</v>
+      </c>
+      <c r="H27">
+        <v>102000000</v>
+      </c>
+      <c r="I27">
+        <v>0.09</v>
+      </c>
+      <c r="J27">
+        <v>2.5000000000000001E-2</v>
+      </c>
+      <c r="K27">
+        <v>22000</v>
+      </c>
+      <c r="L27">
+        <v>0.82</v>
+      </c>
+      <c r="M27">
+        <v>0.96</v>
+      </c>
+      <c r="N27" s="2">
+        <v>0.23</v>
+      </c>
+      <c r="O27" s="2"/>
+    </row>
+    <row r="28" spans="1:15" ht="18">
+      <c r="A28">
+        <v>27</v>
+      </c>
+      <c r="B28" t="s">
+        <v>66</v>
+      </c>
+      <c r="C28" t="s">
+        <v>67</v>
+      </c>
+      <c r="D28">
+        <v>0.78</v>
+      </c>
+      <c r="E28">
+        <v>0.85</v>
+      </c>
+      <c r="F28" t="s">
+        <v>141</v>
+      </c>
+      <c r="G28">
+        <v>79000000</v>
+      </c>
+      <c r="H28">
+        <v>135000000</v>
+      </c>
+      <c r="I28">
+        <v>0.1</v>
+      </c>
+      <c r="J28">
+        <v>0.03</v>
+      </c>
+      <c r="K28">
+        <v>25000</v>
+      </c>
+      <c r="L28">
+        <v>0.9</v>
+      </c>
+      <c r="M28">
+        <v>0.98</v>
+      </c>
+      <c r="N28" s="2">
+        <v>0.26</v>
+      </c>
+      <c r="O28" s="2"/>
+    </row>
+    <row r="29" spans="1:15" ht="18">
+      <c r="A29">
+        <v>28</v>
+      </c>
+      <c r="B29" t="s">
+        <v>79</v>
+      </c>
+      <c r="C29" t="s">
+        <v>31</v>
+      </c>
+      <c r="D29">
+        <v>0.82</v>
+      </c>
+      <c r="E29">
+        <v>0.65</v>
+      </c>
+      <c r="F29" t="s">
+        <v>142</v>
+      </c>
+      <c r="G29">
+        <v>15000000</v>
+      </c>
+      <c r="H29">
+        <v>35000000</v>
+      </c>
+      <c r="I29">
+        <v>0.1</v>
+      </c>
+      <c r="J29">
+        <v>0.05</v>
+      </c>
+      <c r="K29">
+        <v>12000</v>
+      </c>
+      <c r="L29">
+        <v>0.88</v>
+      </c>
+      <c r="M29">
+        <v>0.88</v>
+      </c>
+      <c r="N29" s="2">
+        <v>0.31</v>
+      </c>
+      <c r="O29" s="2"/>
+    </row>
+    <row r="30" spans="1:15" ht="18">
+      <c r="A30">
+        <v>29</v>
+      </c>
+      <c r="B30" t="s">
+        <v>81</v>
+      </c>
+      <c r="C30" t="s">
+        <v>31</v>
+      </c>
+      <c r="D30">
+        <v>0.7</v>
+      </c>
+      <c r="E30">
+        <v>0.62</v>
+      </c>
+      <c r="F30" t="s">
+        <v>143</v>
+      </c>
+      <c r="G30">
+        <v>12000000</v>
+      </c>
+      <c r="H30">
+        <v>30000000</v>
+      </c>
+      <c r="I30">
+        <v>0.09</v>
+      </c>
+      <c r="J30">
+        <v>0.05</v>
+      </c>
+      <c r="K30">
+        <v>11000</v>
+      </c>
+      <c r="L30">
+        <v>0.85</v>
+      </c>
+      <c r="M30">
+        <v>0.85</v>
+      </c>
+      <c r="N30" s="2">
+        <v>0.31</v>
+      </c>
+      <c r="O30" s="2"/>
+    </row>
+    <row r="31" spans="1:15" ht="18">
+      <c r="A31">
+        <v>30</v>
+      </c>
+      <c r="B31" t="s">
+        <v>88</v>
+      </c>
+      <c r="C31" t="s">
+        <v>42</v>
+      </c>
+      <c r="D31">
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="E31">
+        <v>0.6</v>
+      </c>
+      <c r="F31" t="s">
+        <v>144</v>
+      </c>
+      <c r="G31">
+        <v>125000000</v>
+      </c>
+      <c r="H31">
+        <v>84070000</v>
+      </c>
+      <c r="I31">
+        <v>0.09</v>
+      </c>
+      <c r="J31">
+        <v>2.5000000000000001E-2</v>
+      </c>
+      <c r="K31">
+        <v>23000</v>
+      </c>
+      <c r="L31">
+        <v>0.8</v>
+      </c>
+      <c r="M31">
+        <v>0.98</v>
+      </c>
+      <c r="N31" s="2">
+        <v>0.23</v>
+      </c>
+      <c r="O31" s="2"/>
+    </row>
+    <row r="32" spans="1:15" ht="18">
+      <c r="A32">
+        <v>31</v>
+      </c>
+      <c r="B32" t="s">
+        <v>98</v>
+      </c>
+      <c r="C32" t="s">
+        <v>108</v>
+      </c>
+      <c r="D32">
+        <v>0.7</v>
+      </c>
+      <c r="E32">
+        <v>0.5</v>
+      </c>
+      <c r="F32" t="s">
+        <v>145</v>
+      </c>
+      <c r="G32">
+        <v>12000000</v>
+      </c>
+      <c r="H32">
+        <v>35000000</v>
+      </c>
+      <c r="I32">
+        <v>0.1</v>
+      </c>
+      <c r="J32">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="K32">
+        <v>11000</v>
+      </c>
+      <c r="L32">
+        <v>0.9</v>
+      </c>
+      <c r="M32">
+        <v>0.85</v>
+      </c>
+      <c r="N32" s="2">
+        <v>0.34</v>
+      </c>
+      <c r="O32" s="2"/>
+    </row>
+    <row r="33" spans="1:15" ht="18">
+      <c r="A33">
+        <v>32</v>
+      </c>
+      <c r="B33" t="s">
+        <v>146</v>
+      </c>
+      <c r="C33" t="s">
+        <v>49</v>
+      </c>
+      <c r="D33">
+        <v>0.68</v>
+      </c>
+      <c r="E33">
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="F33" t="s">
+        <v>126</v>
+      </c>
+      <c r="G33">
+        <v>10000000</v>
+      </c>
+      <c r="H33">
+        <v>32000000</v>
+      </c>
+      <c r="I33">
+        <v>0.09</v>
+      </c>
+      <c r="J33">
+        <v>0.06</v>
+      </c>
+      <c r="K33">
+        <v>10000</v>
+      </c>
+      <c r="L33">
+        <v>0.85</v>
+      </c>
+      <c r="M33">
+        <v>0.83</v>
+      </c>
+      <c r="N33" s="2">
+        <v>0.32</v>
+      </c>
+      <c r="O33" s="2"/>
+    </row>
+    <row r="34" spans="1:15" ht="18">
+      <c r="A34">
+        <v>33</v>
+      </c>
+      <c r="B34" t="s">
+        <v>92</v>
+      </c>
+      <c r="C34" t="s">
+        <v>93</v>
+      </c>
+      <c r="D34">
+        <v>0.76</v>
+      </c>
+      <c r="E34">
+        <v>0.72</v>
+      </c>
+      <c r="F34" t="s">
+        <v>147</v>
+      </c>
+      <c r="G34">
+        <v>63000000</v>
+      </c>
+      <c r="H34">
+        <v>53560000</v>
+      </c>
+      <c r="I34">
+        <v>0.1</v>
+      </c>
+      <c r="J34">
+        <v>0.04</v>
+      </c>
+      <c r="K34">
+        <v>17000</v>
+      </c>
+      <c r="L34">
+        <v>0.88</v>
+      </c>
+      <c r="M34">
+        <v>0.92</v>
+      </c>
+      <c r="N34" s="2">
+        <v>0.28999999999999998</v>
+      </c>
+      <c r="O34" s="2"/>
+    </row>
+    <row r="35" spans="1:15" ht="18">
+      <c r="A35">
+        <v>34</v>
+      </c>
+      <c r="B35" t="s">
         <v>153</v>
       </c>
-    </row>
-    <row r="42" spans="1:6" ht="18" x14ac:dyDescent="0.2">
-      <c r="A42" s="2" t="s">
+      <c r="C35" t="s">
+        <v>31</v>
+      </c>
+      <c r="D35">
+        <v>0.74</v>
+      </c>
+      <c r="E35">
+        <v>0.6</v>
+      </c>
+      <c r="F35" t="s">
         <v>154</v>
       </c>
-      <c r="B42" s="1" t="s">
-        <v>155</v>
-      </c>
-      <c r="C42" s="2" t="s">
-        <v>156</v>
-      </c>
-      <c r="D42" s="2" t="s">
+      <c r="G35">
+        <v>8000000</v>
+      </c>
+      <c r="H35">
+        <v>25000000</v>
+      </c>
+      <c r="I35">
+        <v>0.09</v>
+      </c>
+      <c r="J35">
+        <v>0.06</v>
+      </c>
+      <c r="K35">
+        <v>9000</v>
+      </c>
+      <c r="L35">
+        <v>0.85</v>
+      </c>
+      <c r="M35">
+        <v>0.8</v>
+      </c>
+      <c r="N35" s="2">
+        <v>0.32</v>
+      </c>
+      <c r="O35" s="2"/>
+    </row>
+    <row r="36" spans="1:15" ht="18">
+      <c r="A36">
+        <v>35</v>
+      </c>
+      <c r="B36" t="s">
+        <v>105</v>
+      </c>
+      <c r="C36" t="s">
+        <v>31</v>
+      </c>
+      <c r="D36">
+        <v>0.62</v>
+      </c>
+      <c r="E36">
+        <v>0.25</v>
+      </c>
+      <c r="F36" t="s">
+        <v>161</v>
+      </c>
+      <c r="G36">
+        <v>15000000</v>
+      </c>
+      <c r="H36">
+        <v>41310000</v>
+      </c>
+      <c r="I36">
+        <v>0.08</v>
+      </c>
+      <c r="J36">
+        <v>0.03</v>
+      </c>
+      <c r="K36">
+        <v>13000</v>
+      </c>
+      <c r="L36">
+        <v>0.75</v>
+      </c>
+      <c r="M36">
+        <v>0.9</v>
+      </c>
+      <c r="N36" s="2">
+        <v>0.23</v>
+      </c>
+      <c r="O36" s="2"/>
+    </row>
+    <row r="37" spans="1:15" ht="18">
+      <c r="A37">
+        <v>36</v>
+      </c>
+      <c r="B37" t="s">
+        <v>77</v>
+      </c>
+      <c r="C37" t="s">
+        <v>31</v>
+      </c>
+      <c r="D37">
+        <v>0.68</v>
+      </c>
+      <c r="E37">
+        <v>0.4</v>
+      </c>
+      <c r="F37" t="s">
+        <v>168</v>
+      </c>
+      <c r="G37">
+        <v>11000000</v>
+      </c>
+      <c r="H37">
+        <v>28000000</v>
+      </c>
+      <c r="I37">
+        <v>0.08</v>
+      </c>
+      <c r="J37">
+        <v>0.04</v>
+      </c>
+      <c r="K37">
+        <v>10000</v>
+      </c>
+      <c r="L37">
+        <v>0.8</v>
+      </c>
+      <c r="M37">
+        <v>0.85</v>
+      </c>
+      <c r="N37" s="2">
+        <v>0.26</v>
+      </c>
+      <c r="O37" s="2"/>
+    </row>
+    <row r="38" spans="1:15" ht="18">
+      <c r="A38">
+        <v>37</v>
+      </c>
+      <c r="B38" t="s">
+        <v>75</v>
+      </c>
+      <c r="C38" t="s">
+        <v>31</v>
+      </c>
+      <c r="D38">
+        <v>0.7</v>
+      </c>
+      <c r="E38">
+        <v>0.35</v>
+      </c>
+      <c r="F38" t="s">
+        <v>118</v>
+      </c>
+      <c r="G38">
+        <v>20000000</v>
+      </c>
+      <c r="H38">
+        <v>40000000</v>
+      </c>
+      <c r="I38">
+        <v>0.08</v>
+      </c>
+      <c r="J38">
+        <v>3.5000000000000003E-2</v>
+      </c>
+      <c r="K38">
+        <v>14000</v>
+      </c>
+      <c r="L38">
+        <v>0.78</v>
+      </c>
+      <c r="M38">
+        <v>0.9</v>
+      </c>
+      <c r="N38" s="2">
+        <v>0.24</v>
+      </c>
+      <c r="O38" s="2"/>
+    </row>
+    <row r="39" spans="1:15" ht="18">
+      <c r="A39">
+        <v>38</v>
+      </c>
+      <c r="B39" t="s">
+        <v>90</v>
+      </c>
+      <c r="C39" t="s">
+        <v>31</v>
+      </c>
+      <c r="D39">
+        <v>0.78</v>
+      </c>
+      <c r="E39">
+        <v>0.38</v>
+      </c>
+      <c r="F39" t="s">
+        <v>179</v>
+      </c>
+      <c r="G39">
+        <v>9000000</v>
+      </c>
+      <c r="H39">
+        <v>30000000</v>
+      </c>
+      <c r="I39">
+        <v>0.09</v>
+      </c>
+      <c r="J39">
+        <v>0.05</v>
+      </c>
+      <c r="K39">
+        <v>11000</v>
+      </c>
+      <c r="L39">
+        <v>0.82</v>
+      </c>
+      <c r="M39">
+        <v>0.85</v>
+      </c>
+      <c r="N39" s="2">
+        <v>0.28999999999999998</v>
+      </c>
+      <c r="O39" s="2"/>
+    </row>
+    <row r="40" spans="1:15" ht="18">
+      <c r="A40">
+        <v>39</v>
+      </c>
+      <c r="B40" t="s">
+        <v>86</v>
+      </c>
+      <c r="C40" t="s">
+        <v>31</v>
+      </c>
+      <c r="D40">
+        <v>0.65</v>
+      </c>
+      <c r="E40">
+        <v>0.42</v>
+      </c>
+      <c r="F40" t="s">
+        <v>185</v>
+      </c>
+      <c r="G40">
+        <v>20000000</v>
+      </c>
+      <c r="H40">
+        <v>38060000</v>
+      </c>
+      <c r="I40">
+        <v>0.08</v>
+      </c>
+      <c r="J40">
+        <v>0.03</v>
+      </c>
+      <c r="K40">
+        <v>14000</v>
+      </c>
+      <c r="L40">
+        <v>0.75</v>
+      </c>
+      <c r="M40">
+        <v>0.95</v>
+      </c>
+      <c r="N40" s="2">
+        <v>0.23</v>
+      </c>
+      <c r="O40" s="2"/>
+    </row>
+    <row r="41" spans="1:15" ht="18">
+      <c r="A41">
+        <v>40</v>
+      </c>
+      <c r="B41" t="s">
+        <v>107</v>
+      </c>
+      <c r="C41" t="s">
+        <v>108</v>
+      </c>
+      <c r="D41">
+        <v>0.78</v>
+      </c>
+      <c r="E41">
+        <v>0.6</v>
+      </c>
+      <c r="F41" t="s">
+        <v>191</v>
+      </c>
+      <c r="G41">
+        <v>97000000</v>
+      </c>
+      <c r="H41">
+        <v>96560000</v>
+      </c>
+      <c r="I41">
+        <v>0.09</v>
+      </c>
+      <c r="J41">
+        <v>0.03</v>
+      </c>
+      <c r="K41">
+        <v>22000</v>
+      </c>
+      <c r="L41">
+        <v>0.85</v>
+      </c>
+      <c r="M41">
+        <v>0.97</v>
+      </c>
+      <c r="N41" s="2">
+        <v>0.25</v>
+      </c>
+      <c r="O41" s="2"/>
+    </row>
+    <row r="42" spans="1:15" ht="18">
+      <c r="A42">
+        <v>41</v>
+      </c>
+      <c r="B42" t="s">
+        <v>198</v>
+      </c>
+      <c r="C42" t="s">
+        <v>150</v>
+      </c>
+      <c r="D42" t="s">
+        <v>151</v>
+      </c>
+      <c r="E42" t="s">
+        <v>150</v>
+      </c>
+      <c r="F42" t="s">
+        <v>152</v>
+      </c>
+      <c r="G42">
+        <v>8000000</v>
+      </c>
+      <c r="H42">
+        <v>28000000</v>
+      </c>
+      <c r="I42">
+        <v>0.11</v>
+      </c>
+      <c r="J42">
+        <v>0.08</v>
+      </c>
+      <c r="K42">
+        <v>9000</v>
+      </c>
+      <c r="L42">
+        <v>0.92</v>
+      </c>
+      <c r="M42">
+        <v>0.8</v>
+      </c>
+      <c r="N42" s="2">
+        <v>0.36</v>
+      </c>
+    </row>
+    <row r="43" spans="1:15" ht="18">
+      <c r="A43">
+        <v>42</v>
+      </c>
+      <c r="B43" t="s">
+        <v>203</v>
+      </c>
+      <c r="C43" t="s">
+        <v>150</v>
+      </c>
+      <c r="D43" t="s">
+        <v>151</v>
+      </c>
+      <c r="E43" t="s">
+        <v>150</v>
+      </c>
+      <c r="F43" t="s">
+        <v>152</v>
+      </c>
+      <c r="G43">
+        <v>7000000</v>
+      </c>
+      <c r="H43">
+        <v>25000000</v>
+      </c>
+      <c r="I43">
+        <v>0.1</v>
+      </c>
+      <c r="J43">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="K43">
+        <v>8500</v>
+      </c>
+      <c r="L43">
+        <v>0.85</v>
+      </c>
+      <c r="M43">
+        <v>0.78</v>
+      </c>
+      <c r="N43" s="2">
+        <v>0.33</v>
+      </c>
+    </row>
+    <row r="44" spans="1:15" ht="18">
+      <c r="A44">
+        <v>43</v>
+      </c>
+      <c r="B44" t="s">
+        <v>208</v>
+      </c>
+      <c r="C44" t="s">
+        <v>150</v>
+      </c>
+      <c r="D44" t="s">
+        <v>151</v>
+      </c>
+      <c r="E44" t="s">
+        <v>150</v>
+      </c>
+      <c r="F44" t="s">
+        <v>152</v>
+      </c>
+      <c r="G44">
+        <v>6000000</v>
+      </c>
+      <c r="H44">
+        <v>20000000</v>
+      </c>
+      <c r="I44">
+        <v>0.1</v>
+      </c>
+      <c r="J44">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="K44">
+        <v>8000</v>
+      </c>
+      <c r="L44">
+        <v>0.88</v>
+      </c>
+      <c r="M44">
+        <v>0.75</v>
+      </c>
+      <c r="N44" s="2">
+        <v>0.33</v>
+      </c>
+    </row>
+    <row r="45" spans="1:15" ht="18">
+      <c r="A45">
+        <v>44</v>
+      </c>
+      <c r="B45" t="s">
+        <v>209</v>
+      </c>
+      <c r="C45" t="s">
+        <v>150</v>
+      </c>
+      <c r="D45" t="s">
+        <v>151</v>
+      </c>
+      <c r="E45" t="s">
+        <v>150</v>
+      </c>
+      <c r="F45" t="s">
+        <v>152</v>
+      </c>
+      <c r="G45">
+        <v>5000000</v>
+      </c>
+      <c r="H45">
+        <v>18000000</v>
+      </c>
+      <c r="I45">
+        <v>0.11</v>
+      </c>
+      <c r="J45">
+        <v>0.08</v>
+      </c>
+      <c r="K45">
+        <v>7500</v>
+      </c>
+      <c r="L45">
+        <v>0.9</v>
+      </c>
+      <c r="M45">
+        <v>0.75</v>
+      </c>
+      <c r="N45" s="2">
+        <v>0.35</v>
+      </c>
+    </row>
+    <row r="46" spans="1:15" ht="18">
+      <c r="A46">
+        <v>45</v>
+      </c>
+      <c r="B46" t="s">
+        <v>210</v>
+      </c>
+      <c r="C46" t="s">
+        <v>150</v>
+      </c>
+      <c r="D46" t="s">
+        <v>151</v>
+      </c>
+      <c r="E46" t="s">
+        <v>150</v>
+      </c>
+      <c r="F46" t="s">
+        <v>152</v>
+      </c>
+      <c r="G46">
+        <v>9000000</v>
+      </c>
+      <c r="H46">
+        <v>22000000</v>
+      </c>
+      <c r="I46">
+        <v>0.1</v>
+      </c>
+      <c r="J46">
+        <v>0.06</v>
+      </c>
+      <c r="K46">
+        <v>9000</v>
+      </c>
+      <c r="L46">
+        <v>0.85</v>
+      </c>
+      <c r="M46">
+        <v>0.85</v>
+      </c>
+      <c r="N46" s="2">
+        <v>0.31</v>
+      </c>
+    </row>
+    <row r="47" spans="1:15" ht="18">
+      <c r="A47">
+        <v>46</v>
+      </c>
+      <c r="B47" t="s">
+        <v>211</v>
+      </c>
+      <c r="C47" t="s">
+        <v>150</v>
+      </c>
+      <c r="D47" t="s">
+        <v>151</v>
+      </c>
+      <c r="E47" t="s">
+        <v>150</v>
+      </c>
+      <c r="F47" t="s">
+        <v>152</v>
+      </c>
+      <c r="G47">
+        <v>6000000</v>
+      </c>
+      <c r="H47">
+        <v>15000000</v>
+      </c>
+      <c r="I47">
+        <v>0.09</v>
+      </c>
+      <c r="J47">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="K47">
+        <v>7000</v>
+      </c>
+      <c r="L47">
+        <v>0.8</v>
+      </c>
+      <c r="M47">
+        <v>0.8</v>
+      </c>
+      <c r="N47" s="2">
+        <v>0.32</v>
+      </c>
+    </row>
+    <row r="48" spans="1:15" ht="18">
+      <c r="A48">
+        <v>47</v>
+      </c>
+      <c r="B48" t="s">
+        <v>212</v>
+      </c>
+      <c r="C48" t="s">
+        <v>150</v>
+      </c>
+      <c r="D48" t="s">
+        <v>151</v>
+      </c>
+      <c r="E48" t="s">
+        <v>150</v>
+      </c>
+      <c r="F48" t="s">
+        <v>152</v>
+      </c>
+      <c r="G48">
+        <v>5000000</v>
+      </c>
+      <c r="H48">
+        <v>14000000</v>
+      </c>
+      <c r="I48">
+        <v>0.09</v>
+      </c>
+      <c r="J48">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="K48">
+        <v>6500</v>
+      </c>
+      <c r="L48">
+        <v>0.82</v>
+      </c>
+      <c r="M48">
+        <v>0.78</v>
+      </c>
+      <c r="N48" s="2">
+        <v>0.32</v>
+      </c>
+    </row>
+    <row r="49" spans="1:14" ht="18">
+      <c r="A49">
+        <v>48</v>
+      </c>
+      <c r="B49" t="s">
+        <v>214</v>
+      </c>
+      <c r="C49" t="s">
+        <v>150</v>
+      </c>
+      <c r="D49" t="s">
+        <v>151</v>
+      </c>
+      <c r="E49" t="s">
+        <v>150</v>
+      </c>
+      <c r="F49" t="s">
+        <v>152</v>
+      </c>
+      <c r="G49">
+        <v>10000000</v>
+      </c>
+      <c r="H49">
+        <v>30000000</v>
+      </c>
+      <c r="I49">
+        <v>0.1</v>
+      </c>
+      <c r="J49">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="K49">
+        <v>11000</v>
+      </c>
+      <c r="L49">
+        <v>0.88</v>
+      </c>
+      <c r="M49">
+        <v>0.85</v>
+      </c>
+      <c r="N49" s="2">
+        <v>0.33</v>
+      </c>
+    </row>
+    <row r="50" spans="1:14" ht="18">
+      <c r="A50">
+        <v>49</v>
+      </c>
+      <c r="B50" t="s">
+        <v>215</v>
+      </c>
+      <c r="C50" t="s">
+        <v>150</v>
+      </c>
+      <c r="D50" t="s">
+        <v>151</v>
+      </c>
+      <c r="E50" t="s">
+        <v>150</v>
+      </c>
+      <c r="F50" t="s">
+        <v>152</v>
+      </c>
+      <c r="G50">
+        <v>8000000</v>
+      </c>
+      <c r="H50">
+        <v>22000000</v>
+      </c>
+      <c r="I50">
+        <v>0.09</v>
+      </c>
+      <c r="J50">
+        <v>0.06</v>
+      </c>
+      <c r="K50">
+        <v>9000</v>
+      </c>
+      <c r="L50">
+        <v>0.85</v>
+      </c>
+      <c r="M50">
+        <v>0.8</v>
+      </c>
+      <c r="N50" s="2">
+        <v>0.31</v>
+      </c>
+    </row>
+    <row r="51" spans="1:14" ht="18">
+      <c r="A51">
+        <v>50</v>
+      </c>
+      <c r="B51" t="s">
+        <v>216</v>
+      </c>
+      <c r="C51" t="s">
+        <v>150</v>
+      </c>
+      <c r="D51" t="s">
+        <v>151</v>
+      </c>
+      <c r="E51" t="s">
+        <v>150</v>
+      </c>
+      <c r="F51" t="s">
+        <v>152</v>
+      </c>
+      <c r="G51">
+        <v>6000000</v>
+      </c>
+      <c r="H51">
+        <v>18000000</v>
+      </c>
+      <c r="I51">
+        <v>0.1</v>
+      </c>
+      <c r="J51">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="K51">
+        <v>8000</v>
+      </c>
+      <c r="L51">
+        <v>0.87</v>
+      </c>
+      <c r="M51">
+        <v>0.78</v>
+      </c>
+      <c r="N51" s="2">
+        <v>0.33</v>
+      </c>
+    </row>
+    <row r="52" spans="1:14" ht="18">
+      <c r="A52">
+        <v>51</v>
+      </c>
+      <c r="B52" t="s">
+        <v>217</v>
+      </c>
+      <c r="C52" t="s">
         <v>157</v>
       </c>
-      <c r="E42" s="2" t="s">
-        <v>156</v>
-      </c>
-      <c r="F42" s="2" t="s">
+      <c r="D52" t="s">
         <v>158</v>
       </c>
-    </row>
-    <row r="43" spans="1:6" ht="18" x14ac:dyDescent="0.2">
-      <c r="A43" s="2" t="s">
+      <c r="E52" t="s">
         <v>159</v>
       </c>
-      <c r="B43" s="1" t="s">
+      <c r="F52" t="s">
         <v>160</v>
       </c>
-      <c r="C43" s="2" t="s">
-        <v>161</v>
-      </c>
-      <c r="D43" s="2" t="s">
-        <v>162</v>
-      </c>
-      <c r="E43" s="2" t="s">
-        <v>163</v>
-      </c>
-      <c r="F43" s="2" t="s">
+      <c r="G52">
+        <v>5000000</v>
+      </c>
+      <c r="H52">
+        <v>15000000</v>
+      </c>
+      <c r="I52">
+        <v>0.1</v>
+      </c>
+      <c r="J52">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="K52">
+        <v>7500</v>
+      </c>
+      <c r="L52">
+        <v>0.85</v>
+      </c>
+      <c r="M52">
+        <v>0.78</v>
+      </c>
+      <c r="N52" s="2">
+        <v>0.33</v>
+      </c>
+    </row>
+    <row r="53" spans="1:14" ht="18">
+      <c r="A53">
+        <v>52</v>
+      </c>
+      <c r="B53" t="s">
+        <v>218</v>
+      </c>
+      <c r="C53" t="s">
+        <v>157</v>
+      </c>
+      <c r="D53" t="s">
+        <v>158</v>
+      </c>
+      <c r="E53" t="s">
+        <v>159</v>
+      </c>
+      <c r="F53" t="s">
+        <v>160</v>
+      </c>
+      <c r="G53">
+        <v>20000000</v>
+      </c>
+      <c r="H53">
+        <v>40000000</v>
+      </c>
+      <c r="I53">
+        <v>0.1</v>
+      </c>
+      <c r="J53">
+        <v>0.05</v>
+      </c>
+      <c r="K53">
+        <v>14000</v>
+      </c>
+      <c r="L53">
+        <v>0.85</v>
+      </c>
+      <c r="M53">
+        <v>0.9</v>
+      </c>
+      <c r="N53" s="2">
+        <v>0.28999999999999998</v>
+      </c>
+    </row>
+    <row r="54" spans="1:14" ht="18">
+      <c r="A54">
+        <v>53</v>
+      </c>
+      <c r="B54" t="s">
+        <v>219</v>
+      </c>
+      <c r="C54" t="s">
+        <v>157</v>
+      </c>
+      <c r="D54" t="s">
+        <v>158</v>
+      </c>
+      <c r="E54" t="s">
+        <v>159</v>
+      </c>
+      <c r="F54" t="s">
+        <v>160</v>
+      </c>
+      <c r="G54">
+        <v>25000000</v>
+      </c>
+      <c r="H54">
+        <v>45000000</v>
+      </c>
+      <c r="I54">
+        <v>0.1</v>
+      </c>
+      <c r="J54">
+        <v>0.05</v>
+      </c>
+      <c r="K54">
+        <v>15000</v>
+      </c>
+      <c r="L54">
+        <v>0.88</v>
+      </c>
+      <c r="M54">
+        <v>0.9</v>
+      </c>
+      <c r="N54" s="2">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="55" spans="1:14" ht="18">
+      <c r="A55">
+        <v>54</v>
+      </c>
+      <c r="B55" t="s">
+        <v>220</v>
+      </c>
+      <c r="C55" t="s">
+        <v>157</v>
+      </c>
+      <c r="D55" t="s">
+        <v>158</v>
+      </c>
+      <c r="E55" t="s">
+        <v>159</v>
+      </c>
+      <c r="F55" t="s">
+        <v>160</v>
+      </c>
+      <c r="G55">
+        <v>22000000</v>
+      </c>
+      <c r="H55">
+        <v>42000000</v>
+      </c>
+      <c r="I55">
+        <v>0.1</v>
+      </c>
+      <c r="J55">
+        <v>0.05</v>
+      </c>
+      <c r="K55">
+        <v>14000</v>
+      </c>
+      <c r="L55">
+        <v>0.88</v>
+      </c>
+      <c r="M55">
+        <v>0.9</v>
+      </c>
+      <c r="N55" s="2">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="56" spans="1:14" ht="18">
+      <c r="A56">
+        <v>55</v>
+      </c>
+      <c r="B56" t="s">
+        <v>221</v>
+      </c>
+      <c r="C56" t="s">
+        <v>157</v>
+      </c>
+      <c r="D56" t="s">
+        <v>158</v>
+      </c>
+      <c r="E56" t="s">
+        <v>159</v>
+      </c>
+      <c r="F56" t="s">
+        <v>160</v>
+      </c>
+      <c r="G56">
+        <v>12000000</v>
+      </c>
+      <c r="H56">
+        <v>30000000</v>
+      </c>
+      <c r="I56">
+        <v>0.1</v>
+      </c>
+      <c r="J56">
+        <v>0.06</v>
+      </c>
+      <c r="K56">
+        <v>11000</v>
+      </c>
+      <c r="L56">
+        <v>0.85</v>
+      </c>
+      <c r="M56">
+        <v>0.85</v>
+      </c>
+      <c r="N56" s="2">
+        <v>0.31</v>
+      </c>
+    </row>
+    <row r="57" spans="1:14" ht="18">
+      <c r="A57">
+        <v>56</v>
+      </c>
+      <c r="B57" t="s">
+        <v>222</v>
+      </c>
+      <c r="C57" t="s">
+        <v>157</v>
+      </c>
+      <c r="D57" t="s">
+        <v>158</v>
+      </c>
+      <c r="E57" t="s">
+        <v>159</v>
+      </c>
+      <c r="F57" t="s">
+        <v>160</v>
+      </c>
+      <c r="G57">
+        <v>11000000</v>
+      </c>
+      <c r="H57">
+        <v>28000000</v>
+      </c>
+      <c r="I57">
+        <v>0.1</v>
+      </c>
+      <c r="J57">
+        <v>0.06</v>
+      </c>
+      <c r="K57">
+        <v>10000</v>
+      </c>
+      <c r="L57">
+        <v>0.85</v>
+      </c>
+      <c r="M57">
+        <v>0.85</v>
+      </c>
+      <c r="N57" s="2">
+        <v>0.31</v>
+      </c>
+    </row>
+    <row r="58" spans="1:14" ht="18">
+      <c r="A58">
+        <v>57</v>
+      </c>
+      <c r="B58" t="s">
+        <v>223</v>
+      </c>
+      <c r="C58" t="s">
+        <v>157</v>
+      </c>
+      <c r="D58" t="s">
+        <v>158</v>
+      </c>
+      <c r="E58" t="s">
+        <v>159</v>
+      </c>
+      <c r="F58" t="s">
+        <v>160</v>
+      </c>
+      <c r="G58">
+        <v>10000000</v>
+      </c>
+      <c r="H58">
+        <v>27000000</v>
+      </c>
+      <c r="I58">
+        <v>0.09</v>
+      </c>
+      <c r="J58">
+        <v>0.06</v>
+      </c>
+      <c r="K58">
+        <v>10000</v>
+      </c>
+      <c r="L58">
+        <v>0.82</v>
+      </c>
+      <c r="M58">
+        <v>0.85</v>
+      </c>
+      <c r="N58" s="2">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="59" spans="1:14" ht="18">
+      <c r="A59">
+        <v>58</v>
+      </c>
+      <c r="B59" t="s">
+        <v>224</v>
+      </c>
+      <c r="C59" t="s">
+        <v>157</v>
+      </c>
+      <c r="D59" t="s">
+        <v>158</v>
+      </c>
+      <c r="E59" t="s">
+        <v>159</v>
+      </c>
+      <c r="F59" t="s">
+        <v>160</v>
+      </c>
+      <c r="G59">
+        <v>11000000</v>
+      </c>
+      <c r="H59">
+        <v>30000000</v>
+      </c>
+      <c r="I59">
+        <v>0.1</v>
+      </c>
+      <c r="J59">
+        <v>0.06</v>
+      </c>
+      <c r="K59">
+        <v>11000</v>
+      </c>
+      <c r="L59">
+        <v>0.85</v>
+      </c>
+      <c r="M59">
+        <v>0.85</v>
+      </c>
+      <c r="N59" s="2">
+        <v>0.31</v>
+      </c>
+    </row>
+    <row r="60" spans="1:14" ht="18">
+      <c r="A60">
+        <v>59</v>
+      </c>
+      <c r="B60" t="s">
+        <v>225</v>
+      </c>
+      <c r="C60" t="s">
+        <v>157</v>
+      </c>
+      <c r="D60" t="s">
+        <v>158</v>
+      </c>
+      <c r="E60" t="s">
+        <v>159</v>
+      </c>
+      <c r="F60" t="s">
+        <v>160</v>
+      </c>
+      <c r="G60">
+        <v>12000000</v>
+      </c>
+      <c r="H60">
+        <v>32000000</v>
+      </c>
+      <c r="I60">
+        <v>0.1</v>
+      </c>
+      <c r="J60">
+        <v>0.06</v>
+      </c>
+      <c r="K60">
+        <v>11000</v>
+      </c>
+      <c r="L60">
+        <v>0.85</v>
+      </c>
+      <c r="M60">
+        <v>0.85</v>
+      </c>
+      <c r="N60" s="2">
+        <v>0.31</v>
+      </c>
+    </row>
+    <row r="61" spans="1:14" ht="18">
+      <c r="A61">
+        <v>60</v>
+      </c>
+      <c r="B61" t="s">
+        <v>226</v>
+      </c>
+      <c r="C61" t="s">
+        <v>157</v>
+      </c>
+      <c r="D61" t="s">
+        <v>158</v>
+      </c>
+      <c r="E61" t="s">
+        <v>159</v>
+      </c>
+      <c r="F61" t="s">
+        <v>160</v>
+      </c>
+      <c r="G61">
+        <v>4000000</v>
+      </c>
+      <c r="H61">
+        <v>15000000</v>
+      </c>
+      <c r="I61">
+        <v>0.11</v>
+      </c>
+      <c r="J61">
+        <v>0.08</v>
+      </c>
+      <c r="K61">
+        <v>7000</v>
+      </c>
+      <c r="L61">
+        <v>0.9</v>
+      </c>
+      <c r="M61">
+        <v>0.75</v>
+      </c>
+      <c r="N61" s="2">
+        <v>0.35</v>
+      </c>
+    </row>
+    <row r="62" spans="1:14" ht="18">
+      <c r="A62">
+        <v>61</v>
+      </c>
+      <c r="B62" t="s">
+        <v>227</v>
+      </c>
+      <c r="C62" t="s">
         <v>164</v>
       </c>
-    </row>
-    <row r="44" spans="1:6" ht="18" x14ac:dyDescent="0.2">
-      <c r="A44" s="2" t="s">
+      <c r="D62" t="s">
         <v>165</v>
       </c>
-      <c r="B44" s="1" t="s">
+      <c r="E62" t="s">
         <v>166</v>
       </c>
-      <c r="C44" s="2" t="s">
+      <c r="F62" t="s">
         <v>167</v>
       </c>
-      <c r="D44" s="2" t="s">
-        <v>168</v>
-      </c>
-      <c r="E44" s="2" t="s">
-        <v>169</v>
-      </c>
-      <c r="F44" s="2" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="45" spans="1:6" ht="18" x14ac:dyDescent="0.2">
-      <c r="A45" s="2" t="s">
+      <c r="G62">
+        <v>9000000</v>
+      </c>
+      <c r="H62">
+        <v>20000000</v>
+      </c>
+      <c r="I62">
+        <v>0.1</v>
+      </c>
+      <c r="J62">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="K62">
+        <v>9000</v>
+      </c>
+      <c r="L62">
+        <v>0.9</v>
+      </c>
+      <c r="M62">
+        <v>0.82</v>
+      </c>
+      <c r="N62" s="2">
+        <v>0.34</v>
+      </c>
+    </row>
+    <row r="63" spans="1:14" ht="18">
+      <c r="A63">
+        <v>62</v>
+      </c>
+      <c r="B63" t="s">
+        <v>228</v>
+      </c>
+      <c r="C63" t="s">
+        <v>164</v>
+      </c>
+      <c r="D63" t="s">
+        <v>165</v>
+      </c>
+      <c r="E63" t="s">
+        <v>166</v>
+      </c>
+      <c r="F63" t="s">
+        <v>167</v>
+      </c>
+      <c r="G63">
+        <v>15000000</v>
+      </c>
+      <c r="H63">
+        <v>25000000</v>
+      </c>
+      <c r="I63">
+        <v>0.11</v>
+      </c>
+      <c r="J63">
+        <v>0.08</v>
+      </c>
+      <c r="K63">
+        <v>10000</v>
+      </c>
+      <c r="L63">
+        <v>0.95</v>
+      </c>
+      <c r="M63">
+        <v>0.88</v>
+      </c>
+      <c r="N63" s="2">
+        <v>0.37</v>
+      </c>
+    </row>
+    <row r="64" spans="1:14" ht="18">
+      <c r="A64">
+        <v>63</v>
+      </c>
+      <c r="B64" t="s">
+        <v>229</v>
+      </c>
+      <c r="C64" t="s">
+        <v>164</v>
+      </c>
+      <c r="D64" t="s">
+        <v>165</v>
+      </c>
+      <c r="E64" t="s">
+        <v>166</v>
+      </c>
+      <c r="F64" t="s">
+        <v>167</v>
+      </c>
+      <c r="G64" s="2">
+        <v>20000000</v>
+      </c>
+      <c r="H64" s="2">
+        <v>30000000</v>
+      </c>
+      <c r="I64" s="2">
+        <v>0.1</v>
+      </c>
+      <c r="J64" s="2">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="K64" s="2">
+        <v>11000</v>
+      </c>
+      <c r="L64" s="2">
+        <v>0.9</v>
+      </c>
+      <c r="M64" s="2">
+        <v>0.9</v>
+      </c>
+      <c r="N64" s="2">
+        <v>0.33</v>
+      </c>
+    </row>
+    <row r="65" spans="1:14" ht="18">
+      <c r="A65">
+        <v>64</v>
+      </c>
+      <c r="B65" t="s">
+        <v>230</v>
+      </c>
+      <c r="C65" t="s">
+        <v>164</v>
+      </c>
+      <c r="D65" t="s">
+        <v>165</v>
+      </c>
+      <c r="E65" t="s">
+        <v>166</v>
+      </c>
+      <c r="F65" t="s">
+        <v>167</v>
+      </c>
+      <c r="G65" s="2">
+        <v>12000000</v>
+      </c>
+      <c r="H65" s="2">
+        <v>22000000</v>
+      </c>
+      <c r="I65" s="2">
+        <v>0.1</v>
+      </c>
+      <c r="J65" s="2">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="K65" s="2">
+        <v>9000</v>
+      </c>
+      <c r="L65" s="2">
+        <v>0.92</v>
+      </c>
+      <c r="M65" s="2">
+        <v>0.85</v>
+      </c>
+      <c r="N65" s="2">
+        <v>0.34</v>
+      </c>
+    </row>
+    <row r="66" spans="1:14" ht="18">
+      <c r="A66">
+        <v>65</v>
+      </c>
+      <c r="B66" t="s">
+        <v>231</v>
+      </c>
+      <c r="C66" t="s">
+        <v>164</v>
+      </c>
+      <c r="D66" t="s">
+        <v>165</v>
+      </c>
+      <c r="E66" t="s">
+        <v>166</v>
+      </c>
+      <c r="F66" t="s">
+        <v>167</v>
+      </c>
+      <c r="G66" s="2">
+        <v>18000000</v>
+      </c>
+      <c r="H66" s="2">
+        <v>28000000</v>
+      </c>
+      <c r="I66" s="2">
+        <v>0.1</v>
+      </c>
+      <c r="J66" s="2">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="K66" s="2">
+        <v>11000</v>
+      </c>
+      <c r="L66" s="2">
+        <v>0.9</v>
+      </c>
+      <c r="M66" s="2">
+        <v>0.88</v>
+      </c>
+      <c r="N66" s="2">
+        <v>0.33</v>
+      </c>
+    </row>
+    <row r="67" spans="1:14" ht="18">
+      <c r="A67">
+        <v>66</v>
+      </c>
+      <c r="B67" t="s">
+        <v>232</v>
+      </c>
+      <c r="C67" t="s">
+        <v>164</v>
+      </c>
+      <c r="D67" t="s">
+        <v>165</v>
+      </c>
+      <c r="E67" t="s">
+        <v>166</v>
+      </c>
+      <c r="F67" t="s">
+        <v>167</v>
+      </c>
+      <c r="G67" s="2">
+        <v>15000000</v>
+      </c>
+      <c r="H67" s="2">
+        <v>26000000</v>
+      </c>
+      <c r="I67" s="2">
+        <v>0.1</v>
+      </c>
+      <c r="J67" s="2">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="K67" s="2">
+        <v>10000</v>
+      </c>
+      <c r="L67" s="2">
+        <v>0.9</v>
+      </c>
+      <c r="M67" s="2">
+        <v>0.88</v>
+      </c>
+      <c r="N67" s="2">
+        <v>0.33</v>
+      </c>
+    </row>
+    <row r="68" spans="1:14" ht="18">
+      <c r="A68">
+        <v>67</v>
+      </c>
+      <c r="B68" t="s">
+        <v>233</v>
+      </c>
+      <c r="C68" t="s">
+        <v>164</v>
+      </c>
+      <c r="D68" t="s">
+        <v>165</v>
+      </c>
+      <c r="E68" t="s">
+        <v>166</v>
+      </c>
+      <c r="F68" t="s">
+        <v>167</v>
+      </c>
+      <c r="G68" s="2">
+        <v>7000000</v>
+      </c>
+      <c r="H68" s="2">
+        <v>18000000</v>
+      </c>
+      <c r="I68" s="2">
+        <v>0.1</v>
+      </c>
+      <c r="J68" s="2">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="K68" s="2">
+        <v>8000</v>
+      </c>
+      <c r="L68" s="2">
+        <v>0.85</v>
+      </c>
+      <c r="M68" s="2">
+        <v>0.8</v>
+      </c>
+      <c r="N68" s="2">
+        <v>0.33</v>
+      </c>
+    </row>
+    <row r="69" spans="1:14" ht="18">
+      <c r="A69">
+        <v>68</v>
+      </c>
+      <c r="B69" t="s">
+        <v>234</v>
+      </c>
+      <c r="C69" t="s">
+        <v>164</v>
+      </c>
+      <c r="D69" t="s">
+        <v>165</v>
+      </c>
+      <c r="E69" t="s">
+        <v>166</v>
+      </c>
+      <c r="F69" t="s">
+        <v>167</v>
+      </c>
+      <c r="G69" s="2">
+        <v>12000000</v>
+      </c>
+      <c r="H69" s="2">
+        <v>20000000</v>
+      </c>
+      <c r="I69" s="2">
+        <v>0.09</v>
+      </c>
+      <c r="J69" s="2">
+        <v>0.05</v>
+      </c>
+      <c r="K69" s="2">
+        <v>9000</v>
+      </c>
+      <c r="L69" s="2">
+        <v>0.8</v>
+      </c>
+      <c r="M69" s="2">
+        <v>0.85</v>
+      </c>
+      <c r="N69" s="2">
+        <v>0.28000000000000003</v>
+      </c>
+    </row>
+    <row r="70" spans="1:14" ht="18">
+      <c r="A70">
+        <v>69</v>
+      </c>
+      <c r="B70" t="s">
+        <v>235</v>
+      </c>
+      <c r="C70" t="s">
+        <v>164</v>
+      </c>
+      <c r="D70" t="s">
+        <v>165</v>
+      </c>
+      <c r="E70" t="s">
+        <v>166</v>
+      </c>
+      <c r="F70" t="s">
+        <v>167</v>
+      </c>
+      <c r="G70" s="2">
+        <v>8000000</v>
+      </c>
+      <c r="H70" s="2">
+        <v>15000000</v>
+      </c>
+      <c r="I70" s="2">
+        <v>0.09</v>
+      </c>
+      <c r="J70" s="2">
+        <v>0.05</v>
+      </c>
+      <c r="K70" s="2">
+        <v>8000</v>
+      </c>
+      <c r="L70" s="2">
+        <v>0.8</v>
+      </c>
+      <c r="M70" s="2">
+        <v>0.82</v>
+      </c>
+      <c r="N70" s="2">
+        <v>0.28000000000000003</v>
+      </c>
+    </row>
+    <row r="71" spans="1:14" ht="18">
+      <c r="A71">
+        <v>70</v>
+      </c>
+      <c r="B71" t="s">
+        <v>236</v>
+      </c>
+      <c r="C71" t="s">
+        <v>164</v>
+      </c>
+      <c r="D71" t="s">
+        <v>165</v>
+      </c>
+      <c r="E71" t="s">
+        <v>166</v>
+      </c>
+      <c r="F71" t="s">
+        <v>167</v>
+      </c>
+      <c r="G71" s="2">
+        <v>5000000</v>
+      </c>
+      <c r="H71" s="2">
+        <v>12000000</v>
+      </c>
+      <c r="I71" s="2">
+        <v>0.1</v>
+      </c>
+      <c r="J71" s="2">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="K71" s="2">
+        <v>7000</v>
+      </c>
+      <c r="L71" s="2">
+        <v>0.85</v>
+      </c>
+      <c r="M71" s="2">
+        <v>0.78</v>
+      </c>
+      <c r="N71" s="2">
+        <v>0.33</v>
+      </c>
+    </row>
+    <row r="72" spans="1:14" ht="18">
+      <c r="A72">
+        <v>71</v>
+      </c>
+      <c r="B72" t="s">
+        <v>237</v>
+      </c>
+      <c r="C72" t="s">
+        <v>164</v>
+      </c>
+      <c r="D72" t="s">
+        <v>165</v>
+      </c>
+      <c r="E72" t="s">
+        <v>166</v>
+      </c>
+      <c r="F72" t="s">
+        <v>167</v>
+      </c>
+      <c r="G72" s="2">
+        <v>9000000</v>
+      </c>
+      <c r="H72" s="2">
+        <v>20000000</v>
+      </c>
+      <c r="I72" s="2">
+        <v>0.09</v>
+      </c>
+      <c r="J72" s="2">
+        <v>0.05</v>
+      </c>
+      <c r="K72" s="2">
+        <v>9000</v>
+      </c>
+      <c r="L72" s="2">
+        <v>0.8</v>
+      </c>
+      <c r="M72" s="2">
+        <v>0.85</v>
+      </c>
+      <c r="N72" s="2">
+        <v>0.28000000000000003</v>
+      </c>
+    </row>
+    <row r="73" spans="1:14" ht="18">
+      <c r="A73">
+        <v>72</v>
+      </c>
+      <c r="B73" t="s">
+        <v>238</v>
+      </c>
+      <c r="C73" t="s">
+        <v>164</v>
+      </c>
+      <c r="D73" t="s">
+        <v>165</v>
+      </c>
+      <c r="E73" t="s">
+        <v>166</v>
+      </c>
+      <c r="F73" t="s">
+        <v>167</v>
+      </c>
+      <c r="G73" s="2">
+        <v>6000000</v>
+      </c>
+      <c r="H73" s="2">
+        <v>15000000</v>
+      </c>
+      <c r="I73" s="2">
+        <v>0.1</v>
+      </c>
+      <c r="J73" s="2">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="K73" s="2">
+        <v>8000</v>
+      </c>
+      <c r="L73" s="2">
+        <v>0.88</v>
+      </c>
+      <c r="M73" s="2">
+        <v>0.8</v>
+      </c>
+      <c r="N73" s="2">
+        <v>0.33</v>
+      </c>
+    </row>
+    <row r="74" spans="1:14" ht="18">
+      <c r="A74">
+        <v>73</v>
+      </c>
+      <c r="B74" t="s">
+        <v>239</v>
+      </c>
+      <c r="C74" t="s">
+        <v>164</v>
+      </c>
+      <c r="D74" t="s">
+        <v>165</v>
+      </c>
+      <c r="E74" t="s">
+        <v>166</v>
+      </c>
+      <c r="F74" t="s">
+        <v>167</v>
+      </c>
+      <c r="G74" s="2">
+        <v>8000000</v>
+      </c>
+      <c r="H74" s="2">
+        <v>18000000</v>
+      </c>
+      <c r="I74" s="2">
+        <v>0.1</v>
+      </c>
+      <c r="J74" s="2">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="K74" s="2">
+        <v>8500</v>
+      </c>
+      <c r="L74" s="2">
+        <v>0.85</v>
+      </c>
+      <c r="M74" s="2">
+        <v>0.8</v>
+      </c>
+      <c r="N74" s="2">
+        <v>0.33</v>
+      </c>
+    </row>
+    <row r="75" spans="1:14" ht="18">
+      <c r="A75">
+        <v>74</v>
+      </c>
+      <c r="B75" t="s">
+        <v>240</v>
+      </c>
+      <c r="C75" t="s">
+        <v>164</v>
+      </c>
+      <c r="D75" t="s">
+        <v>165</v>
+      </c>
+      <c r="E75" t="s">
+        <v>166</v>
+      </c>
+      <c r="F75" t="s">
+        <v>167</v>
+      </c>
+      <c r="G75" s="2">
+        <v>10000000</v>
+      </c>
+      <c r="H75" s="2">
+        <v>22000000</v>
+      </c>
+      <c r="I75" s="2">
+        <v>0.09</v>
+      </c>
+      <c r="J75" s="2">
+        <v>0.05</v>
+      </c>
+      <c r="K75" s="2">
+        <v>9500</v>
+      </c>
+      <c r="L75" s="2">
+        <v>0.82</v>
+      </c>
+      <c r="M75" s="2">
+        <v>0.85</v>
+      </c>
+      <c r="N75" s="2">
+        <v>0.28000000000000003</v>
+      </c>
+    </row>
+    <row r="76" spans="1:14" ht="18">
+      <c r="A76">
+        <v>75</v>
+      </c>
+      <c r="B76" t="s">
+        <v>241</v>
+      </c>
+      <c r="C76" t="s">
+        <v>164</v>
+      </c>
+      <c r="D76" t="s">
+        <v>165</v>
+      </c>
+      <c r="E76" t="s">
+        <v>166</v>
+      </c>
+      <c r="F76" t="s">
+        <v>167</v>
+      </c>
+      <c r="G76" s="2">
+        <v>9000000</v>
+      </c>
+      <c r="H76" s="2">
+        <v>20000000</v>
+      </c>
+      <c r="I76" s="2">
+        <v>0.09</v>
+      </c>
+      <c r="J76" s="2">
+        <v>0.05</v>
+      </c>
+      <c r="K76" s="2">
+        <v>9000</v>
+      </c>
+      <c r="L76" s="2">
+        <v>0.82</v>
+      </c>
+      <c r="M76" s="2">
+        <v>0.85</v>
+      </c>
+      <c r="N76" s="2">
+        <v>0.28000000000000003</v>
+      </c>
+    </row>
+    <row r="77" spans="1:14" ht="18">
+      <c r="A77">
+        <v>76</v>
+      </c>
+      <c r="B77" t="s">
+        <v>242</v>
+      </c>
+      <c r="C77" t="s">
+        <v>13</v>
+      </c>
+      <c r="D77" t="s">
+        <v>159</v>
+      </c>
+      <c r="E77" t="s">
         <v>171</v>
       </c>
-      <c r="B45" s="1" t="s">
+      <c r="F77" t="s">
         <v>172</v>
       </c>
-      <c r="C45" s="2" t="s">
+      <c r="G77" s="2">
+        <v>8000000</v>
+      </c>
+      <c r="H77" s="2">
+        <v>20000000</v>
+      </c>
+      <c r="I77" s="2">
+        <v>0.09</v>
+      </c>
+      <c r="J77" s="2">
+        <v>0.06</v>
+      </c>
+      <c r="K77" s="2">
+        <v>9000</v>
+      </c>
+      <c r="L77" s="2">
+        <v>0.75</v>
+      </c>
+      <c r="M77" s="2">
+        <v>0.85</v>
+      </c>
+      <c r="N77" s="2">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="78" spans="1:14" ht="18">
+      <c r="A78">
+        <v>77</v>
+      </c>
+      <c r="B78" t="s">
+        <v>243</v>
+      </c>
+      <c r="C78" t="s">
         <v>13</v>
       </c>
-      <c r="D45" s="2" t="s">
-        <v>163</v>
-      </c>
-      <c r="E45" s="2" t="s">
-        <v>173</v>
-      </c>
-      <c r="F45" s="2" t="s">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="46" spans="1:6" ht="18" x14ac:dyDescent="0.2">
-      <c r="A46" s="2" t="s">
+      <c r="D78" t="s">
+        <v>159</v>
+      </c>
+      <c r="E78" t="s">
+        <v>171</v>
+      </c>
+      <c r="F78" t="s">
+        <v>172</v>
+      </c>
+      <c r="G78" s="2">
+        <v>9000000</v>
+      </c>
+      <c r="H78" s="2">
+        <v>22000000</v>
+      </c>
+      <c r="I78" s="2">
+        <v>0.09</v>
+      </c>
+      <c r="J78" s="2">
+        <v>0.06</v>
+      </c>
+      <c r="K78" s="2">
+        <v>9000</v>
+      </c>
+      <c r="L78" s="2">
+        <v>0.75</v>
+      </c>
+      <c r="M78" s="2">
+        <v>0.85</v>
+      </c>
+      <c r="N78" s="2">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="79" spans="1:14" ht="18">
+      <c r="A79">
+        <v>78</v>
+      </c>
+      <c r="B79" t="s">
+        <v>244</v>
+      </c>
+      <c r="C79" t="s">
+        <v>13</v>
+      </c>
+      <c r="D79" t="s">
+        <v>159</v>
+      </c>
+      <c r="E79" t="s">
+        <v>171</v>
+      </c>
+      <c r="F79" t="s">
+        <v>172</v>
+      </c>
+      <c r="G79" s="2">
+        <v>7000000</v>
+      </c>
+      <c r="H79" s="2">
+        <v>18000000</v>
+      </c>
+      <c r="I79" s="2">
+        <v>0.09</v>
+      </c>
+      <c r="J79" s="2">
+        <v>0.06</v>
+      </c>
+      <c r="K79" s="2">
+        <v>8000</v>
+      </c>
+      <c r="L79" s="2">
+        <v>0.75</v>
+      </c>
+      <c r="M79" s="2">
+        <v>0.8</v>
+      </c>
+      <c r="N79" s="2">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="80" spans="1:14" ht="18">
+      <c r="A80">
+        <v>79</v>
+      </c>
+      <c r="B80" t="s">
+        <v>245</v>
+      </c>
+      <c r="C80" t="s">
+        <v>13</v>
+      </c>
+      <c r="D80" t="s">
+        <v>159</v>
+      </c>
+      <c r="E80" t="s">
+        <v>171</v>
+      </c>
+      <c r="F80" t="s">
+        <v>172</v>
+      </c>
+      <c r="G80" s="2">
+        <v>6000000</v>
+      </c>
+      <c r="H80" s="2">
+        <v>15000000</v>
+      </c>
+      <c r="I80" s="2">
+        <v>0.09</v>
+      </c>
+      <c r="J80" s="2">
+        <v>0.06</v>
+      </c>
+      <c r="K80" s="2">
+        <v>7500</v>
+      </c>
+      <c r="L80" s="2">
+        <v>0.75</v>
+      </c>
+      <c r="M80" s="2">
+        <v>0.8</v>
+      </c>
+      <c r="N80" s="2">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="81" spans="1:14" ht="18">
+      <c r="A81">
+        <v>80</v>
+      </c>
+      <c r="B81" t="s">
+        <v>246</v>
+      </c>
+      <c r="C81" t="s">
+        <v>13</v>
+      </c>
+      <c r="D81" t="s">
+        <v>159</v>
+      </c>
+      <c r="E81" t="s">
+        <v>171</v>
+      </c>
+      <c r="F81" t="s">
+        <v>172</v>
+      </c>
+      <c r="G81" s="2">
+        <v>6000000</v>
+      </c>
+      <c r="H81" s="2">
+        <v>15000000</v>
+      </c>
+      <c r="I81" s="2">
+        <v>0.09</v>
+      </c>
+      <c r="J81" s="2">
+        <v>0.06</v>
+      </c>
+      <c r="K81" s="2">
+        <v>7500</v>
+      </c>
+      <c r="L81" s="2">
+        <v>0.75</v>
+      </c>
+      <c r="M81" s="2">
+        <v>0.8</v>
+      </c>
+      <c r="N81" s="2">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="82" spans="1:14" ht="18">
+      <c r="A82">
+        <v>81</v>
+      </c>
+      <c r="B82" t="s">
+        <v>247</v>
+      </c>
+      <c r="C82" t="s">
+        <v>13</v>
+      </c>
+      <c r="D82" t="s">
+        <v>159</v>
+      </c>
+      <c r="E82" t="s">
+        <v>171</v>
+      </c>
+      <c r="F82" t="s">
+        <v>172</v>
+      </c>
+      <c r="G82" s="2">
+        <v>5000000</v>
+      </c>
+      <c r="H82" s="2">
+        <v>14000000</v>
+      </c>
+      <c r="I82" s="2">
+        <v>0.1</v>
+      </c>
+      <c r="J82" s="2">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="K82" s="2">
+        <v>7000</v>
+      </c>
+      <c r="L82" s="2">
+        <v>0.8</v>
+      </c>
+      <c r="M82" s="2">
+        <v>0.78</v>
+      </c>
+      <c r="N82" s="2">
+        <v>0.32</v>
+      </c>
+    </row>
+    <row r="83" spans="1:14" ht="18">
+      <c r="A83">
+        <v>82</v>
+      </c>
+      <c r="B83" t="s">
+        <v>248</v>
+      </c>
+      <c r="C83" t="s">
+        <v>13</v>
+      </c>
+      <c r="D83" t="s">
+        <v>159</v>
+      </c>
+      <c r="E83" t="s">
+        <v>171</v>
+      </c>
+      <c r="F83" t="s">
+        <v>172</v>
+      </c>
+      <c r="G83" s="2">
+        <v>12000000</v>
+      </c>
+      <c r="H83" s="2">
+        <v>30000000</v>
+      </c>
+      <c r="I83" s="2">
+        <v>0.09</v>
+      </c>
+      <c r="J83" s="2">
+        <v>0.05</v>
+      </c>
+      <c r="K83" s="2">
+        <v>11000</v>
+      </c>
+      <c r="L83" s="2">
+        <v>0.75</v>
+      </c>
+      <c r="M83" s="2">
+        <v>0.88</v>
+      </c>
+      <c r="N83" s="2">
+        <v>0.28000000000000003</v>
+      </c>
+    </row>
+    <row r="84" spans="1:14" ht="18">
+      <c r="A84">
+        <v>83</v>
+      </c>
+      <c r="B84" t="s">
+        <v>249</v>
+      </c>
+      <c r="C84" t="s">
+        <v>13</v>
+      </c>
+      <c r="D84" t="s">
+        <v>159</v>
+      </c>
+      <c r="E84" t="s">
+        <v>171</v>
+      </c>
+      <c r="F84" t="s">
+        <v>172</v>
+      </c>
+      <c r="G84" s="2">
+        <v>9000000</v>
+      </c>
+      <c r="H84" s="2">
+        <v>25000000</v>
+      </c>
+      <c r="I84" s="2">
+        <v>0.09</v>
+      </c>
+      <c r="J84" s="2">
+        <v>0.05</v>
+      </c>
+      <c r="K84" s="2">
+        <v>10000</v>
+      </c>
+      <c r="L84" s="2">
+        <v>0.75</v>
+      </c>
+      <c r="M84" s="2">
+        <v>0.85</v>
+      </c>
+      <c r="N84" s="2">
+        <v>0.28000000000000003</v>
+      </c>
+    </row>
+    <row r="85" spans="1:14" ht="18">
+      <c r="A85">
+        <v>84</v>
+      </c>
+      <c r="B85" t="s">
+        <v>250</v>
+      </c>
+      <c r="C85" t="s">
+        <v>13</v>
+      </c>
+      <c r="D85" t="s">
+        <v>159</v>
+      </c>
+      <c r="E85" t="s">
+        <v>171</v>
+      </c>
+      <c r="F85" t="s">
+        <v>172</v>
+      </c>
+      <c r="G85" s="2">
+        <v>8000000</v>
+      </c>
+      <c r="H85" s="2">
+        <v>22000000</v>
+      </c>
+      <c r="I85" s="2">
+        <v>0.09</v>
+      </c>
+      <c r="J85" s="2">
+        <v>0.05</v>
+      </c>
+      <c r="K85" s="2">
+        <v>9500</v>
+      </c>
+      <c r="L85" s="2">
+        <v>0.75</v>
+      </c>
+      <c r="M85" s="2">
+        <v>0.85</v>
+      </c>
+      <c r="N85" s="2">
+        <v>0.28000000000000003</v>
+      </c>
+    </row>
+    <row r="86" spans="1:14" ht="18">
+      <c r="A86">
+        <v>85</v>
+      </c>
+      <c r="B86" t="s">
+        <v>251</v>
+      </c>
+      <c r="C86" t="s">
+        <v>13</v>
+      </c>
+      <c r="D86" t="s">
+        <v>159</v>
+      </c>
+      <c r="E86" t="s">
+        <v>171</v>
+      </c>
+      <c r="F86" t="s">
+        <v>172</v>
+      </c>
+      <c r="G86" s="2">
+        <v>15000000</v>
+      </c>
+      <c r="H86" s="2">
+        <v>35000000</v>
+      </c>
+      <c r="I86" s="2">
+        <v>0.09</v>
+      </c>
+      <c r="J86" s="2">
+        <v>0.04</v>
+      </c>
+      <c r="K86" s="2">
+        <v>12000</v>
+      </c>
+      <c r="L86" s="2">
+        <v>0.75</v>
+      </c>
+      <c r="M86" s="2">
+        <v>0.9</v>
+      </c>
+      <c r="N86" s="2">
+        <v>0.27</v>
+      </c>
+    </row>
+    <row r="87" spans="1:14" ht="18">
+      <c r="A87">
+        <v>86</v>
+      </c>
+      <c r="B87" t="s">
+        <v>252</v>
+      </c>
+      <c r="C87" t="s">
+        <v>13</v>
+      </c>
+      <c r="D87" t="s">
+        <v>159</v>
+      </c>
+      <c r="E87" t="s">
+        <v>171</v>
+      </c>
+      <c r="F87" t="s">
+        <v>172</v>
+      </c>
+      <c r="G87" s="2">
+        <v>8000000</v>
+      </c>
+      <c r="H87" s="2">
+        <v>20000000</v>
+      </c>
+      <c r="I87" s="2">
+        <v>0.09</v>
+      </c>
+      <c r="J87" s="2">
+        <v>0.05</v>
+      </c>
+      <c r="K87" s="2">
+        <v>9000</v>
+      </c>
+      <c r="L87" s="2">
+        <v>0.75</v>
+      </c>
+      <c r="M87" s="2">
+        <v>0.85</v>
+      </c>
+      <c r="N87" s="2">
+        <v>0.28000000000000003</v>
+      </c>
+    </row>
+    <row r="88" spans="1:14" ht="18">
+      <c r="A88">
+        <v>87</v>
+      </c>
+      <c r="B88" t="s">
+        <v>253</v>
+      </c>
+      <c r="C88" t="s">
+        <v>13</v>
+      </c>
+      <c r="D88" t="s">
+        <v>159</v>
+      </c>
+      <c r="E88" t="s">
+        <v>171</v>
+      </c>
+      <c r="F88" t="s">
+        <v>172</v>
+      </c>
+      <c r="G88" s="2">
+        <v>7000000</v>
+      </c>
+      <c r="H88" s="2">
+        <v>18000000</v>
+      </c>
+      <c r="I88" s="2">
+        <v>0.09</v>
+      </c>
+      <c r="J88" s="2">
+        <v>0.05</v>
+      </c>
+      <c r="K88" s="2">
+        <v>8500</v>
+      </c>
+      <c r="L88" s="2">
+        <v>0.75</v>
+      </c>
+      <c r="M88" s="2">
+        <v>0.85</v>
+      </c>
+      <c r="N88" s="2">
+        <v>0.28000000000000003</v>
+      </c>
+    </row>
+    <row r="89" spans="1:14" ht="18">
+      <c r="A89">
+        <v>88</v>
+      </c>
+      <c r="B89" t="s">
+        <v>254</v>
+      </c>
+      <c r="C89" t="s">
+        <v>13</v>
+      </c>
+      <c r="D89" t="s">
+        <v>159</v>
+      </c>
+      <c r="E89" t="s">
+        <v>171</v>
+      </c>
+      <c r="F89" t="s">
+        <v>172</v>
+      </c>
+      <c r="G89" s="2">
+        <v>8000000</v>
+      </c>
+      <c r="H89" s="2">
+        <v>20000000</v>
+      </c>
+      <c r="I89" s="2">
+        <v>0.09</v>
+      </c>
+      <c r="J89" s="2">
+        <v>0.05</v>
+      </c>
+      <c r="K89" s="2">
+        <v>9000</v>
+      </c>
+      <c r="L89" s="2">
+        <v>0.75</v>
+      </c>
+      <c r="M89" s="2">
+        <v>0.85</v>
+      </c>
+      <c r="N89" s="2">
+        <v>0.28000000000000003</v>
+      </c>
+    </row>
+    <row r="90" spans="1:14" ht="18">
+      <c r="A90">
+        <v>89</v>
+      </c>
+      <c r="B90" t="s">
+        <v>255</v>
+      </c>
+      <c r="C90" t="s">
+        <v>13</v>
+      </c>
+      <c r="D90" t="s">
+        <v>159</v>
+      </c>
+      <c r="E90" t="s">
+        <v>171</v>
+      </c>
+      <c r="F90" t="s">
+        <v>172</v>
+      </c>
+      <c r="G90" s="2">
+        <v>7000000</v>
+      </c>
+      <c r="H90" s="2">
+        <v>18000000</v>
+      </c>
+      <c r="I90" s="2">
+        <v>0.09</v>
+      </c>
+      <c r="J90" s="2">
+        <v>0.05</v>
+      </c>
+      <c r="K90" s="2">
+        <v>8500</v>
+      </c>
+      <c r="L90" s="2">
+        <v>0.75</v>
+      </c>
+      <c r="M90" s="2">
+        <v>0.85</v>
+      </c>
+      <c r="N90" s="2">
+        <v>0.28000000000000003</v>
+      </c>
+    </row>
+    <row r="91" spans="1:14" ht="18">
+      <c r="A91">
+        <v>90</v>
+      </c>
+      <c r="B91" t="s">
+        <v>256</v>
+      </c>
+      <c r="C91" t="s">
+        <v>13</v>
+      </c>
+      <c r="D91" t="s">
+        <v>159</v>
+      </c>
+      <c r="E91" t="s">
+        <v>171</v>
+      </c>
+      <c r="F91" t="s">
+        <v>172</v>
+      </c>
+      <c r="G91" s="2">
+        <v>10000000</v>
+      </c>
+      <c r="H91" s="2">
+        <v>25000000</v>
+      </c>
+      <c r="I91" s="2">
+        <v>0.09</v>
+      </c>
+      <c r="J91" s="2">
+        <v>0.05</v>
+      </c>
+      <c r="K91" s="2">
+        <v>10000</v>
+      </c>
+      <c r="L91" s="2">
+        <v>0.78</v>
+      </c>
+      <c r="M91" s="2">
+        <v>0.88</v>
+      </c>
+      <c r="N91" s="2">
+        <v>0.28000000000000003</v>
+      </c>
+    </row>
+    <row r="92" spans="1:14" ht="18">
+      <c r="A92">
+        <v>91</v>
+      </c>
+      <c r="B92" t="s">
+        <v>257</v>
+      </c>
+      <c r="C92" t="s">
         <v>175</v>
       </c>
-      <c r="B46" s="1" t="s">
+      <c r="D92" t="s">
         <v>176</v>
       </c>
-      <c r="C46" s="2" t="s">
+      <c r="E92" t="s">
         <v>177</v>
       </c>
-      <c r="D46" s="2" t="s">
+      <c r="F92" t="s">
         <v>178</v>
       </c>
-      <c r="E46" s="2" t="s">
-        <v>179</v>
-      </c>
-      <c r="F46" s="2" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="47" spans="1:6" ht="18" x14ac:dyDescent="0.2">
-      <c r="A47" s="2" t="s">
-        <v>181</v>
-      </c>
-      <c r="B47" s="1" t="s">
-        <v>182</v>
-      </c>
-      <c r="C47" s="2" t="s">
-        <v>183</v>
-      </c>
-      <c r="D47" s="2" t="s">
-        <v>179</v>
-      </c>
-      <c r="E47" s="2" t="s">
-        <v>184</v>
-      </c>
-      <c r="F47" s="2" t="s">
-        <v>185</v>
-      </c>
-    </row>
-    <row r="48" spans="1:6" ht="18" x14ac:dyDescent="0.2">
-      <c r="A48" s="2" t="s">
-        <v>186</v>
-      </c>
-      <c r="B48" s="1" t="s">
-        <v>187</v>
-      </c>
-      <c r="C48" s="2" t="s">
-        <v>188</v>
-      </c>
-      <c r="D48" s="2" t="s">
-        <v>189</v>
-      </c>
-      <c r="E48" s="2" t="s">
-        <v>168</v>
-      </c>
-      <c r="F48" s="2" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="49" spans="1:6" ht="18" x14ac:dyDescent="0.2">
-      <c r="A49" s="2" t="s">
-        <v>191</v>
-      </c>
-      <c r="B49" s="1" t="s">
-        <v>192</v>
-      </c>
-      <c r="C49" s="2" t="s">
-        <v>193</v>
-      </c>
-      <c r="D49" s="2" t="s">
-        <v>194</v>
-      </c>
-      <c r="E49" s="2" t="s">
-        <v>195</v>
-      </c>
-      <c r="F49" s="2" t="s">
-        <v>196</v>
-      </c>
-    </row>
-    <row r="50" spans="1:6" ht="18" x14ac:dyDescent="0.2">
-      <c r="A50" s="2" t="s">
-        <v>197</v>
-      </c>
-      <c r="B50" s="1" t="s">
-        <v>198</v>
-      </c>
-      <c r="C50" s="2" t="s">
-        <v>199</v>
-      </c>
-      <c r="D50" s="2" t="s">
-        <v>163</v>
-      </c>
-      <c r="E50" s="2" t="s">
-        <v>173</v>
-      </c>
-      <c r="F50" s="2" t="s">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="51" spans="1:6" ht="18" x14ac:dyDescent="0.2">
-      <c r="A51" s="2" t="s">
-        <v>201</v>
-      </c>
-      <c r="B51" s="1" t="s">
-        <v>202</v>
-      </c>
-      <c r="C51" s="2" t="s">
-        <v>203</v>
-      </c>
-      <c r="D51" s="2" t="s">
-        <v>173</v>
-      </c>
-      <c r="E51" s="2" t="s">
-        <v>168</v>
-      </c>
-      <c r="F51" s="2" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="52" spans="1:6" ht="18" x14ac:dyDescent="0.2">
-      <c r="B52" s="1"/>
+      <c r="G92" s="2">
+        <v>12000000</v>
+      </c>
+      <c r="H92" s="2">
+        <v>30000000</v>
+      </c>
+      <c r="I92" s="2">
+        <v>0.09</v>
+      </c>
+      <c r="J92" s="2">
+        <v>0.05</v>
+      </c>
+      <c r="K92" s="2">
+        <v>11000</v>
+      </c>
+      <c r="L92" s="2">
+        <v>0.85</v>
+      </c>
+      <c r="M92" s="2">
+        <v>0.88</v>
+      </c>
+      <c r="N92" s="2">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="93" spans="1:14" ht="18">
+      <c r="A93">
+        <v>92</v>
+      </c>
+      <c r="B93" t="s">
+        <v>258</v>
+      </c>
+      <c r="C93" t="s">
+        <v>175</v>
+      </c>
+      <c r="D93" t="s">
+        <v>176</v>
+      </c>
+      <c r="E93" t="s">
+        <v>177</v>
+      </c>
+      <c r="F93" t="s">
+        <v>178</v>
+      </c>
+      <c r="G93" s="2">
+        <v>10000000</v>
+      </c>
+      <c r="H93" s="2">
+        <v>25000000</v>
+      </c>
+      <c r="I93" s="2">
+        <v>0.09</v>
+      </c>
+      <c r="J93" s="2">
+        <v>0.05</v>
+      </c>
+      <c r="K93" s="2">
+        <v>10000</v>
+      </c>
+      <c r="L93" s="2">
+        <v>0.8</v>
+      </c>
+      <c r="M93" s="2">
+        <v>0.85</v>
+      </c>
+      <c r="N93" s="2">
+        <v>0.28999999999999998</v>
+      </c>
+    </row>
+    <row r="94" spans="1:14" ht="18">
+      <c r="A94">
+        <v>93</v>
+      </c>
+      <c r="B94" t="s">
+        <v>259</v>
+      </c>
+      <c r="C94" t="s">
+        <v>175</v>
+      </c>
+      <c r="D94" t="s">
+        <v>176</v>
+      </c>
+      <c r="E94" t="s">
+        <v>177</v>
+      </c>
+      <c r="F94" t="s">
+        <v>178</v>
+      </c>
+      <c r="G94" s="2">
+        <v>9000000</v>
+      </c>
+      <c r="H94" s="2">
+        <v>22000000</v>
+      </c>
+      <c r="I94" s="2">
+        <v>0.09</v>
+      </c>
+      <c r="J94" s="2">
+        <v>0.05</v>
+      </c>
+      <c r="K94" s="2">
+        <v>9500</v>
+      </c>
+      <c r="L94" s="2">
+        <v>0.8</v>
+      </c>
+      <c r="M94" s="2">
+        <v>0.85</v>
+      </c>
+      <c r="N94" s="2">
+        <v>0.28999999999999998</v>
+      </c>
+    </row>
+    <row r="95" spans="1:14" ht="18">
+      <c r="A95">
+        <v>94</v>
+      </c>
+      <c r="B95" t="s">
+        <v>260</v>
+      </c>
+      <c r="C95" t="s">
+        <v>175</v>
+      </c>
+      <c r="D95" t="s">
+        <v>176</v>
+      </c>
+      <c r="E95" t="s">
+        <v>177</v>
+      </c>
+      <c r="F95" t="s">
+        <v>178</v>
+      </c>
+      <c r="G95" s="2">
+        <v>15000000</v>
+      </c>
+      <c r="H95" s="2">
+        <v>35000000</v>
+      </c>
+      <c r="I95" s="2">
+        <v>0.09</v>
+      </c>
+      <c r="J95" s="2">
+        <v>0.05</v>
+      </c>
+      <c r="K95" s="2">
+        <v>12000</v>
+      </c>
+      <c r="L95" s="2">
+        <v>0.82</v>
+      </c>
+      <c r="M95" s="2">
+        <v>0.9</v>
+      </c>
+      <c r="N95" s="2">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="96" spans="1:14" ht="18">
+      <c r="A96">
+        <v>95</v>
+      </c>
+      <c r="B96" t="s">
+        <v>261</v>
+      </c>
+      <c r="C96" t="s">
+        <v>175</v>
+      </c>
+      <c r="D96" t="s">
+        <v>176</v>
+      </c>
+      <c r="E96" t="s">
+        <v>177</v>
+      </c>
+      <c r="F96" t="s">
+        <v>178</v>
+      </c>
+      <c r="G96" s="2">
+        <v>10000000</v>
+      </c>
+      <c r="H96" s="2">
+        <v>25000000</v>
+      </c>
+      <c r="I96" s="2">
+        <v>0.09</v>
+      </c>
+      <c r="J96" s="2">
+        <v>0.05</v>
+      </c>
+      <c r="K96" s="2">
+        <v>10000</v>
+      </c>
+      <c r="L96" s="2">
+        <v>0.8</v>
+      </c>
+      <c r="M96" s="2">
+        <v>0.85</v>
+      </c>
+      <c r="N96" s="2">
+        <v>0.28999999999999998</v>
+      </c>
+    </row>
+    <row r="97" spans="1:14" ht="18">
+      <c r="A97">
+        <v>96</v>
+      </c>
+      <c r="B97" t="s">
+        <v>262</v>
+      </c>
+      <c r="C97" t="s">
+        <v>175</v>
+      </c>
+      <c r="D97" t="s">
+        <v>176</v>
+      </c>
+      <c r="E97" t="s">
+        <v>177</v>
+      </c>
+      <c r="F97" t="s">
+        <v>178</v>
+      </c>
+      <c r="G97" s="2">
+        <v>12000000</v>
+      </c>
+      <c r="H97" s="2">
+        <v>30000000</v>
+      </c>
+      <c r="I97" s="2">
+        <v>0.09</v>
+      </c>
+      <c r="J97" s="2">
+        <v>0.05</v>
+      </c>
+      <c r="K97" s="2">
+        <v>11000</v>
+      </c>
+      <c r="L97" s="2">
+        <v>0.82</v>
+      </c>
+      <c r="M97" s="2">
+        <v>0.88</v>
+      </c>
+      <c r="N97" s="2">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="98" spans="1:14" ht="18">
+      <c r="A98">
+        <v>97</v>
+      </c>
+      <c r="B98" t="s">
+        <v>263</v>
+      </c>
+      <c r="C98" t="s">
+        <v>175</v>
+      </c>
+      <c r="D98" t="s">
+        <v>176</v>
+      </c>
+      <c r="E98" t="s">
+        <v>177</v>
+      </c>
+      <c r="F98" t="s">
+        <v>178</v>
+      </c>
+      <c r="G98" s="2">
+        <v>11000000</v>
+      </c>
+      <c r="H98" s="2">
+        <v>25000000</v>
+      </c>
+      <c r="I98" s="2">
+        <v>0.09</v>
+      </c>
+      <c r="J98" s="2">
+        <v>0.04</v>
+      </c>
+      <c r="K98" s="2">
+        <v>10000</v>
+      </c>
+      <c r="L98" s="2">
+        <v>0.8</v>
+      </c>
+      <c r="M98" s="2">
+        <v>0.88</v>
+      </c>
+      <c r="N98" s="2">
+        <v>0.28000000000000003</v>
+      </c>
+    </row>
+    <row r="99" spans="1:14" ht="18">
+      <c r="A99">
+        <v>98</v>
+      </c>
+      <c r="B99" t="s">
+        <v>264</v>
+      </c>
+      <c r="C99" t="s">
+        <v>175</v>
+      </c>
+      <c r="D99" t="s">
+        <v>176</v>
+      </c>
+      <c r="E99" t="s">
+        <v>177</v>
+      </c>
+      <c r="F99" t="s">
+        <v>178</v>
+      </c>
+      <c r="G99" s="2">
+        <v>9000000</v>
+      </c>
+      <c r="H99" s="2">
+        <v>20000000</v>
+      </c>
+      <c r="I99" s="2">
+        <v>0.09</v>
+      </c>
+      <c r="J99" s="2">
+        <v>0.05</v>
+      </c>
+      <c r="K99" s="2">
+        <v>9000</v>
+      </c>
+      <c r="L99" s="2">
+        <v>0.82</v>
+      </c>
+      <c r="M99" s="2">
+        <v>0.85</v>
+      </c>
+      <c r="N99" s="2">
+        <v>0.28999999999999998</v>
+      </c>
+    </row>
+    <row r="100" spans="1:14" ht="18">
+      <c r="A100">
+        <v>99</v>
+      </c>
+      <c r="B100" t="s">
+        <v>265</v>
+      </c>
+      <c r="C100" t="s">
+        <v>175</v>
+      </c>
+      <c r="D100" t="s">
+        <v>176</v>
+      </c>
+      <c r="E100" t="s">
+        <v>177</v>
+      </c>
+      <c r="F100" t="s">
+        <v>178</v>
+      </c>
+      <c r="G100" s="2">
+        <v>8000000</v>
+      </c>
+      <c r="H100" s="2">
+        <v>18000000</v>
+      </c>
+      <c r="I100" s="2">
+        <v>0.09</v>
+      </c>
+      <c r="J100" s="2">
+        <v>0.04</v>
+      </c>
+      <c r="K100" s="2">
+        <v>8500</v>
+      </c>
+      <c r="L100" s="2">
+        <v>0.8</v>
+      </c>
+      <c r="M100" s="2">
+        <v>0.85</v>
+      </c>
+      <c r="N100" s="2">
+        <v>0.28000000000000003</v>
+      </c>
+    </row>
+    <row r="101" spans="1:14" ht="18">
+      <c r="A101">
+        <v>100</v>
+      </c>
+      <c r="B101" t="s">
+        <v>266</v>
+      </c>
+      <c r="C101" t="s">
+        <v>175</v>
+      </c>
+      <c r="D101" t="s">
+        <v>176</v>
+      </c>
+      <c r="E101" t="s">
+        <v>177</v>
+      </c>
+      <c r="F101" t="s">
+        <v>178</v>
+      </c>
+      <c r="G101" s="2">
+        <v>7000000</v>
+      </c>
+      <c r="H101" s="2">
+        <v>15000000</v>
+      </c>
+      <c r="I101" s="2">
+        <v>0.1</v>
+      </c>
+      <c r="J101" s="2">
+        <v>0.06</v>
+      </c>
+      <c r="K101" s="2">
+        <v>8000</v>
+      </c>
+      <c r="L101" s="2">
+        <v>0.85</v>
+      </c>
+      <c r="M101" s="2">
+        <v>0.85</v>
+      </c>
+      <c r="N101" s="2">
+        <v>0.31</v>
+      </c>
+    </row>
+    <row r="102" spans="1:14" ht="18">
+      <c r="A102">
+        <v>101</v>
+      </c>
+      <c r="B102" t="s">
+        <v>267</v>
+      </c>
+      <c r="C102" t="s">
+        <v>175</v>
+      </c>
+      <c r="D102" t="s">
+        <v>176</v>
+      </c>
+      <c r="E102" t="s">
+        <v>177</v>
+      </c>
+      <c r="F102" t="s">
+        <v>178</v>
+      </c>
+      <c r="G102" s="2">
+        <v>7000000</v>
+      </c>
+      <c r="H102" s="2">
+        <v>15000000</v>
+      </c>
+      <c r="I102" s="2">
+        <v>0.1</v>
+      </c>
+      <c r="J102" s="2">
+        <v>0.06</v>
+      </c>
+      <c r="K102" s="2">
+        <v>8000</v>
+      </c>
+      <c r="L102" s="2">
+        <v>0.85</v>
+      </c>
+      <c r="M102" s="2">
+        <v>0.85</v>
+      </c>
+      <c r="N102" s="2">
+        <v>0.31</v>
+      </c>
+    </row>
+    <row r="103" spans="1:14" ht="18">
+      <c r="A103">
+        <v>102</v>
+      </c>
+      <c r="B103" t="s">
+        <v>268</v>
+      </c>
+      <c r="C103" t="s">
+        <v>175</v>
+      </c>
+      <c r="D103" t="s">
+        <v>176</v>
+      </c>
+      <c r="E103" t="s">
+        <v>177</v>
+      </c>
+      <c r="F103" t="s">
+        <v>178</v>
+      </c>
+      <c r="G103" s="2">
+        <v>6000000</v>
+      </c>
+      <c r="H103" s="2">
+        <v>14000000</v>
+      </c>
+      <c r="I103" s="2">
+        <v>0.1</v>
+      </c>
+      <c r="J103" s="2">
+        <v>0.06</v>
+      </c>
+      <c r="K103" s="2">
+        <v>7500</v>
+      </c>
+      <c r="L103" s="2">
+        <v>0.85</v>
+      </c>
+      <c r="M103" s="2">
+        <v>0.82</v>
+      </c>
+      <c r="N103" s="2">
+        <v>0.31</v>
+      </c>
+    </row>
+    <row r="104" spans="1:14" ht="18">
+      <c r="A104">
+        <v>103</v>
+      </c>
+      <c r="B104" t="s">
+        <v>269</v>
+      </c>
+      <c r="C104" t="s">
+        <v>175</v>
+      </c>
+      <c r="D104" t="s">
+        <v>176</v>
+      </c>
+      <c r="E104" t="s">
+        <v>177</v>
+      </c>
+      <c r="F104" t="s">
+        <v>178</v>
+      </c>
+      <c r="G104" s="2">
+        <v>8000000</v>
+      </c>
+      <c r="H104" s="2">
+        <v>20000000</v>
+      </c>
+      <c r="I104" s="2">
+        <v>0.11</v>
+      </c>
+      <c r="J104" s="2">
+        <v>0.08</v>
+      </c>
+      <c r="K104" s="2">
+        <v>9000</v>
+      </c>
+      <c r="L104" s="2">
+        <v>0.95</v>
+      </c>
+      <c r="M104" s="2">
+        <v>0.88</v>
+      </c>
+      <c r="N104" s="2">
+        <v>0.37</v>
+      </c>
+    </row>
+    <row r="105" spans="1:14" ht="18">
+      <c r="A105">
+        <v>104</v>
+      </c>
+      <c r="B105" t="s">
+        <v>270</v>
+      </c>
+      <c r="C105" t="s">
+        <v>175</v>
+      </c>
+      <c r="D105" t="s">
+        <v>176</v>
+      </c>
+      <c r="E105" t="s">
+        <v>177</v>
+      </c>
+      <c r="F105" t="s">
+        <v>178</v>
+      </c>
+      <c r="G105" s="2">
+        <v>9000000</v>
+      </c>
+      <c r="H105" s="2">
+        <v>22000000</v>
+      </c>
+      <c r="I105" s="2">
+        <v>0.1</v>
+      </c>
+      <c r="J105" s="2">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="K105" s="2">
+        <v>9000</v>
+      </c>
+      <c r="L105" s="2">
+        <v>0.9</v>
+      </c>
+      <c r="M105" s="2">
+        <v>0.88</v>
+      </c>
+      <c r="N105" s="2">
+        <v>0.34</v>
+      </c>
+    </row>
+    <row r="106" spans="1:14" ht="18">
+      <c r="A106">
+        <v>105</v>
+      </c>
+      <c r="B106" t="s">
+        <v>271</v>
+      </c>
+      <c r="C106" t="s">
+        <v>175</v>
+      </c>
+      <c r="D106" t="s">
+        <v>176</v>
+      </c>
+      <c r="E106" t="s">
+        <v>177</v>
+      </c>
+      <c r="F106" t="s">
+        <v>178</v>
+      </c>
+      <c r="G106" s="2">
+        <v>20000000</v>
+      </c>
+      <c r="H106" s="2">
+        <v>40000000</v>
+      </c>
+      <c r="I106" s="2">
+        <v>0.1</v>
+      </c>
+      <c r="J106" s="2">
+        <v>0.05</v>
+      </c>
+      <c r="K106" s="2">
+        <v>14000</v>
+      </c>
+      <c r="L106" s="2">
+        <v>0.88</v>
+      </c>
+      <c r="M106" s="2">
+        <v>0.92</v>
+      </c>
+      <c r="N106" s="2">
+        <v>0.28999999999999998</v>
+      </c>
+    </row>
+    <row r="107" spans="1:14" ht="18">
+      <c r="A107">
+        <v>106</v>
+      </c>
+      <c r="B107" t="s">
+        <v>272</v>
+      </c>
+      <c r="C107" t="s">
+        <v>175</v>
+      </c>
+      <c r="D107" t="s">
+        <v>176</v>
+      </c>
+      <c r="E107" t="s">
+        <v>177</v>
+      </c>
+      <c r="F107" t="s">
+        <v>178</v>
+      </c>
+      <c r="G107" s="2">
+        <v>18000000</v>
+      </c>
+      <c r="H107" s="2">
+        <v>35000000</v>
+      </c>
+      <c r="I107" s="2">
+        <v>0.1</v>
+      </c>
+      <c r="J107" s="2">
+        <v>0.05</v>
+      </c>
+      <c r="K107" s="2">
+        <v>13000</v>
+      </c>
+      <c r="L107" s="2">
+        <v>0.88</v>
+      </c>
+      <c r="M107" s="2">
+        <v>0.92</v>
+      </c>
+      <c r="N107" s="2">
+        <v>0.28999999999999998</v>
+      </c>
+    </row>
+    <row r="108" spans="1:14" ht="18">
+      <c r="A108">
+        <v>107</v>
+      </c>
+      <c r="B108" t="s">
+        <v>273</v>
+      </c>
+      <c r="C108" t="s">
+        <v>175</v>
+      </c>
+      <c r="D108" t="s">
+        <v>176</v>
+      </c>
+      <c r="E108" t="s">
+        <v>177</v>
+      </c>
+      <c r="F108" t="s">
+        <v>178</v>
+      </c>
+      <c r="G108" s="2">
+        <v>15000000</v>
+      </c>
+      <c r="H108" s="2">
+        <v>30000000</v>
+      </c>
+      <c r="I108" s="2">
+        <v>0.1</v>
+      </c>
+      <c r="J108" s="2">
+        <v>0.06</v>
+      </c>
+      <c r="K108" s="2">
+        <v>12000</v>
+      </c>
+      <c r="L108" s="2">
+        <v>0.9</v>
+      </c>
+      <c r="M108" s="2">
+        <v>0.9</v>
+      </c>
+      <c r="N108" s="2">
+        <v>0.31</v>
+      </c>
+    </row>
+    <row r="109" spans="1:14" ht="18">
+      <c r="A109">
+        <v>108</v>
+      </c>
+      <c r="B109" t="s">
+        <v>274</v>
+      </c>
+      <c r="C109" t="s">
+        <v>175</v>
+      </c>
+      <c r="D109" t="s">
+        <v>176</v>
+      </c>
+      <c r="E109" t="s">
+        <v>177</v>
+      </c>
+      <c r="F109" t="s">
+        <v>178</v>
+      </c>
+      <c r="G109" s="2">
+        <v>12000000</v>
+      </c>
+      <c r="H109" s="2">
+        <v>25000000</v>
+      </c>
+      <c r="I109" s="2">
+        <v>0.1</v>
+      </c>
+      <c r="J109" s="2">
+        <v>0.06</v>
+      </c>
+      <c r="K109" s="2">
+        <v>11000</v>
+      </c>
+      <c r="L109" s="2">
+        <v>0.88</v>
+      </c>
+      <c r="M109" s="2">
+        <v>0.88</v>
+      </c>
+      <c r="N109" s="2">
+        <v>0.31</v>
+      </c>
+    </row>
+    <row r="110" spans="1:14" ht="18">
+      <c r="A110">
+        <v>109</v>
+      </c>
+      <c r="B110" t="s">
+        <v>275</v>
+      </c>
+      <c r="C110" t="s">
+        <v>175</v>
+      </c>
+      <c r="D110" t="s">
+        <v>176</v>
+      </c>
+      <c r="E110" t="s">
+        <v>177</v>
+      </c>
+      <c r="F110" t="s">
+        <v>178</v>
+      </c>
+      <c r="G110" s="2">
+        <v>20000000</v>
+      </c>
+      <c r="H110" s="2">
+        <v>35000000</v>
+      </c>
+      <c r="I110" s="2">
+        <v>0.1</v>
+      </c>
+      <c r="J110" s="2">
+        <v>0.05</v>
+      </c>
+      <c r="K110" s="2">
+        <v>13000</v>
+      </c>
+      <c r="L110" s="2">
+        <v>0.88</v>
+      </c>
+      <c r="M110" s="2">
+        <v>0.92</v>
+      </c>
+      <c r="N110" s="2">
+        <v>0.28999999999999998</v>
+      </c>
+    </row>
+    <row r="111" spans="1:14" ht="18">
+      <c r="A111">
+        <v>110</v>
+      </c>
+      <c r="B111" t="s">
+        <v>276</v>
+      </c>
+      <c r="C111" t="s">
+        <v>175</v>
+      </c>
+      <c r="D111" t="s">
+        <v>176</v>
+      </c>
+      <c r="E111" t="s">
+        <v>177</v>
+      </c>
+      <c r="F111" t="s">
+        <v>178</v>
+      </c>
+      <c r="G111" s="2">
+        <v>10000000</v>
+      </c>
+      <c r="H111" s="2">
+        <v>22000000</v>
+      </c>
+      <c r="I111" s="2">
+        <v>0.1</v>
+      </c>
+      <c r="J111" s="2">
+        <v>0.06</v>
+      </c>
+      <c r="K111" s="2">
+        <v>10000</v>
+      </c>
+      <c r="L111" s="2">
+        <v>0.85</v>
+      </c>
+      <c r="M111" s="2">
+        <v>0.88</v>
+      </c>
+      <c r="N111" s="2">
+        <v>0.31</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:N111" xr:uid="{FF2A96F8-74E3-45A2-AD2F-99E4606A4139}"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1707746D-0F11-364A-B277-D77FAA63C221}">
+  <dimension ref="A1:F21"/>
+  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.95"/>
+  <cols>
+    <col min="2" max="2" width="23.875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="20" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="60" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" ht="18">
+      <c r="A1" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" ht="18">
+      <c r="A2" s="2">
+        <v>1</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>290</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>291</v>
+      </c>
+      <c r="D2" s="2">
+        <v>0.4</v>
+      </c>
+      <c r="E2" s="2">
+        <v>0.35</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" ht="18">
+      <c r="A3" s="2">
+        <v>2</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>293</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="D3" s="2">
+        <v>0.68</v>
+      </c>
+      <c r="E3" s="2">
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" ht="18">
+      <c r="A4" s="2">
+        <v>3</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>247</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>295</v>
+      </c>
+      <c r="D4" s="2">
+        <v>0.72</v>
+      </c>
+      <c r="E4" s="2">
+        <v>0.6</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" ht="18">
+      <c r="A5" s="2">
+        <v>4</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>297</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>298</v>
+      </c>
+      <c r="D5" s="2">
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="E5" s="2">
+        <v>0.42</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" ht="18">
+      <c r="A6" s="2">
+        <v>5</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>300</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="D6" s="2">
+        <v>0.72</v>
+      </c>
+      <c r="E6" s="2">
+        <v>0.68</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" ht="18">
+      <c r="A7" s="2">
+        <v>6</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>302</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D7" s="2">
+        <v>0.57999999999999996</v>
+      </c>
+      <c r="E7" s="2">
+        <v>0.52</v>
+      </c>
+      <c r="F7" s="2" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" ht="18">
+      <c r="A8" s="2">
+        <v>7</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>304</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>305</v>
+      </c>
+      <c r="D8" s="2">
+        <v>0.75</v>
+      </c>
+      <c r="E8" s="2">
+        <v>0.4</v>
+      </c>
+      <c r="F8" s="2" t="s">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" ht="18">
+      <c r="A9" s="2">
+        <v>8</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>307</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>308</v>
+      </c>
+      <c r="D9" s="2">
+        <v>0.85</v>
+      </c>
+      <c r="E9" s="2">
+        <v>0.3</v>
+      </c>
+      <c r="F9" s="2" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" ht="18">
+      <c r="A10" s="2">
+        <v>9</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>310</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>291</v>
+      </c>
+      <c r="D10" s="2">
+        <v>0.5</v>
+      </c>
+      <c r="E10" s="2">
+        <v>0.62</v>
+      </c>
+      <c r="F10" s="2" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" ht="18">
+      <c r="A11" s="2">
+        <v>10</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>312</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>313</v>
+      </c>
+      <c r="D11" s="2">
+        <v>0.78</v>
+      </c>
+      <c r="E11" s="2">
+        <v>0.65</v>
+      </c>
+      <c r="F11" s="2" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" ht="18">
+      <c r="A12" s="2">
+        <v>11</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>315</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D12" s="2">
+        <v>0.65</v>
+      </c>
+      <c r="E12" s="2">
+        <v>0.57999999999999996</v>
+      </c>
+      <c r="F12" s="2" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" ht="18">
+      <c r="A13" s="2">
+        <v>12</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>317</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>318</v>
+      </c>
+      <c r="D13" s="2">
+        <v>0.35</v>
+      </c>
+      <c r="E13" s="2">
+        <v>0.25</v>
+      </c>
+      <c r="F13" s="2" t="s">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" ht="18">
+      <c r="A14" s="2">
+        <v>13</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>320</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>321</v>
+      </c>
+      <c r="D14" s="2">
+        <v>0.45</v>
+      </c>
+      <c r="E14" s="2">
+        <v>0.38</v>
+      </c>
+      <c r="F14" s="2" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" ht="18">
+      <c r="A15" s="2">
+        <v>14</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>323</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>324</v>
+      </c>
+      <c r="D15" s="2">
+        <v>0.72</v>
+      </c>
+      <c r="E15" s="2">
+        <v>0.35</v>
+      </c>
+      <c r="F15" s="2" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" ht="18">
+      <c r="A16" s="2">
+        <v>15</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>326</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="D16" s="2">
+        <v>0.42</v>
+      </c>
+      <c r="E16" s="2">
+        <v>0.5</v>
+      </c>
+      <c r="F16" s="2" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" ht="18">
+      <c r="A17" s="2">
+        <v>16</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>328</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="D17" s="2">
+        <v>0.84</v>
+      </c>
+      <c r="E17" s="2">
+        <v>0.7</v>
+      </c>
+      <c r="F17" s="2" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" ht="18">
+      <c r="A18" s="2">
+        <v>17</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>330</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>331</v>
+      </c>
+      <c r="D18" s="2">
+        <v>0.62</v>
+      </c>
+      <c r="E18" s="2">
+        <v>0.48</v>
+      </c>
+      <c r="F18" s="2" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" ht="18">
+      <c r="A19" s="2">
+        <v>18</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>333</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>334</v>
+      </c>
+      <c r="D19" s="2">
+        <v>0.45</v>
+      </c>
+      <c r="E19" s="2">
+        <v>0.4</v>
+      </c>
+      <c r="F19" s="2" t="s">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" ht="18">
+      <c r="A20" s="2">
+        <v>19</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>336</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>337</v>
+      </c>
+      <c r="D20" s="2">
+        <v>0.57999999999999996</v>
+      </c>
+      <c r="E20" s="2">
+        <v>0.5</v>
+      </c>
+      <c r="F20" s="2" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" ht="18">
+      <c r="A21" s="2">
+        <v>20</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>339</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>340</v>
+      </c>
+      <c r="D21" s="2">
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="E21" s="2">
+        <v>0.48</v>
+      </c>
+      <c r="F21" s="2" t="s">
+        <v>341</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
